--- a/ROSALES/Agosto/expensas rosales Agosto.xlsx
+++ b/ROSALES/Agosto/expensas rosales Agosto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD9D3A01-D2A7-49FB-844C-698F75106640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DF8DE0-3354-44D4-97EB-043BB8634CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Edesur" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$66</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$N$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$L$37</definedName>
   </definedNames>
@@ -386,9 +386,6 @@
     <t>Brian</t>
   </si>
   <si>
-    <t>PREVISION EXTRAORDINARIA GASTOS A DEFINIR EN ASAMBLEA</t>
-  </si>
-  <si>
     <t>Gastos extraordinarios:</t>
   </si>
   <si>
@@ -435,17 +432,20 @@
     <t>ARBA</t>
   </si>
   <si>
-    <t xml:space="preserve">Adelanto pago 1 terraza </t>
-  </si>
-  <si>
-    <t>Compra de materiales - Techos 25 de mayo - Obra terraza</t>
-  </si>
-  <si>
-    <t>LAS LINEAS GRSISES CORRESPONDEN A PLANES DE PAGO VIGENTES</t>
-  </si>
-  <si>
     <t>ATENCIÓN: Al momento de abonar en efectivo las expensas (dado que no se dispone de cuenta bancaria), deberán cancelar el monto total correspondiente, que incluye tanto las expensas como el consumo de Edesur de cada unidad funcional.
 Les recordamos que el pago debe realizarse con dinero justo.</t>
+  </si>
+  <si>
+    <t>PREVISION EXTRAORDINARIA</t>
+  </si>
+  <si>
+    <t>LAS LINEAS GRISES CORRESPONDEN A PLANES DE PAGO VIGENTES -  RESTA ABONAR 6 CUOTAS DE $107.386,20 + LAS EXPENSAS AL DIA - PARTE DE LA DEUDA CANCELA EDESUR Y EXPENSAS CON TASA DE INTERES MENSUAL</t>
+  </si>
+  <si>
+    <t>ADELANTO PAGO 1 - TERRAZA</t>
+  </si>
+  <si>
+    <t>COMPRA DE MATERIALES TECHO - OBRA TERRAZA</t>
   </si>
 </sst>
 </file>
@@ -467,7 +467,7 @@
     <numFmt numFmtId="174" formatCode="_-* #,##0.000000_-;\-* #,##0.000000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="175" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -672,14 +672,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -774,7 +766,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1063,98 +1055,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1163,7 +1063,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="237">
+  <cellXfs count="230">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1405,16 +1305,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="11" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1448,7 +1339,6 @@
     </xf>
     <xf numFmtId="172" fontId="25" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="172" fontId="25" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="172" fontId="25" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="20" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1459,39 +1349,6 @@
     <xf numFmtId="175" fontId="9" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="20" fillId="6" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="19" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1527,9 +1384,21 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="11" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="26" fillId="11" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="172" fontId="32" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1537,10 +1406,36 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="172" fontId="33" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1958,7 +1853,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F68"/>
+  <dimension ref="A2:F67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1996,10 +1891,10 @@
         <v>25</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2048,10 +1943,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B18" s="38"/>
-      <c r="C18" s="193">
+      <c r="C18" s="33">
         <v>76654</v>
       </c>
       <c r="D18" s="4"/>
@@ -2062,7 +1957,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="194">
+      <c r="C19" s="223">
         <v>321313.76</v>
       </c>
       <c r="D19" s="20"/>
@@ -2070,10 +1965,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B20" s="39"/>
-      <c r="C20" s="194">
+      <c r="C20" s="223">
         <v>571077.30000000005</v>
       </c>
       <c r="D20" s="20"/>
@@ -2084,7 +1979,7 @@
         <v>26</v>
       </c>
       <c r="B21" s="39"/>
-      <c r="C21" s="193">
+      <c r="C21" s="33">
         <v>77800</v>
       </c>
       <c r="D21" s="20"/>
@@ -2092,10 +1987,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B22" s="39"/>
-      <c r="C22" s="193">
+      <c r="C22" s="33">
         <v>14856</v>
       </c>
       <c r="D22" s="20"/>
@@ -2108,13 +2003,13 @@
       <c r="B23" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="193">
+      <c r="C23" s="33">
         <v>83400</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6"/>
       <c r="F23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2130,14 +2025,14 @@
         <v>12</v>
       </c>
       <c r="B25" s="39"/>
-      <c r="C25" s="188"/>
+      <c r="C25" s="178"/>
     </row>
     <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
         <v>114</v>
       </c>
       <c r="B26" s="42"/>
-      <c r="C26" s="193">
+      <c r="C26" s="33">
         <f>349151.87+ (349151.87*10%)</f>
         <v>384067.05699999997</v>
       </c>
@@ -2149,319 +2044,311 @@
         <v>115</v>
       </c>
       <c r="B27" s="42"/>
-      <c r="C27" s="193">
+      <c r="C27" s="33">
         <v>5684</v>
       </c>
       <c r="D27" s="45"/>
       <c r="F27" s="12"/>
     </row>
     <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="186" t="s">
-        <v>135</v>
+      <c r="A28" s="176" t="s">
+        <v>125</v>
       </c>
       <c r="B28" s="140"/>
-      <c r="C28" s="193">
-        <v>400000</v>
+      <c r="C28" s="33">
+        <v>49940</v>
       </c>
       <c r="D28" s="45"/>
       <c r="F28" s="12"/>
     </row>
     <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="186" t="s">
-        <v>136</v>
-      </c>
-      <c r="B29" s="140"/>
-      <c r="C29" s="193">
-        <v>307000</v>
-      </c>
-      <c r="D29" s="45"/>
+      <c r="A29" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="B29" s="42"/>
+      <c r="C29" s="33">
+        <v>45000</v>
+      </c>
       <c r="F29" s="12"/>
     </row>
     <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="186" t="s">
-        <v>126</v>
-      </c>
-      <c r="B30" s="140"/>
-      <c r="C30" s="193">
-        <v>49940</v>
-      </c>
-      <c r="D30" s="45"/>
+      <c r="A30" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B30" s="39"/>
+      <c r="C30" s="34">
+        <v>300000</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="6"/>
       <c r="F30" s="12"/>
     </row>
     <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="B31" s="42"/>
-      <c r="C31" s="193">
-        <v>45000</v>
+      <c r="A31" s="40"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="23">
+        <f>SUM(C25:C30)</f>
+        <v>784691.05700000003</v>
       </c>
       <c r="F31" s="12"/>
     </row>
     <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="B32" s="39"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="6"/>
+      <c r="A32" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="30"/>
+      <c r="C32" s="43">
+        <f>+C31+C24</f>
+        <v>1929792.1170000001</v>
+      </c>
       <c r="F32" s="12"/>
     </row>
     <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="40"/>
-      <c r="B33" s="41"/>
-      <c r="C33" s="23">
-        <f>SUM(C25:C32)</f>
-        <v>1191691.057</v>
-      </c>
+      <c r="C33" s="24"/>
       <c r="F33" s="12"/>
     </row>
     <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="30"/>
-      <c r="C34" s="43">
-        <f>+C33+C24</f>
-        <v>2336792.1170000001</v>
-      </c>
+      <c r="A34" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="24"/>
       <c r="F34" s="12"/>
     </row>
     <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C35" s="24"/>
+      <c r="A35" s="28"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="33"/>
       <c r="F35" s="12"/>
     </row>
     <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C36" s="24"/>
+      <c r="A36" s="28"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="34"/>
       <c r="F36" s="12"/>
     </row>
     <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="28"/>
       <c r="B37" s="28"/>
-      <c r="C37" s="33"/>
+      <c r="C37" s="34"/>
       <c r="F37" s="12"/>
     </row>
     <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="28"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="34"/>
+      <c r="C38" s="25"/>
       <c r="F38" s="12"/>
     </row>
     <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="28"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="34"/>
+      <c r="A39" s="179" t="s">
+        <v>135</v>
+      </c>
+      <c r="B39" s="179"/>
+      <c r="C39" s="180"/>
       <c r="F39" s="12"/>
     </row>
     <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C40" s="25"/>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="189" t="s">
-        <v>119</v>
-      </c>
-      <c r="B41" s="189"/>
-      <c r="C41" s="190">
-        <v>1000000</v>
-      </c>
-      <c r="F41" s="12"/>
-    </row>
-    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C42" s="25"/>
-      <c r="F42" s="12"/>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="14">
+        <f>+C35+C36+C37+C40</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="6"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="14">
-        <f>+C37+C38+C39+C42</f>
-        <v>0</v>
-      </c>
-      <c r="E43" s="6"/>
+      <c r="A43" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" s="18"/>
+      <c r="C43" s="19">
+        <f>+C41+C32</f>
+        <v>1929792.1170000001</v>
+      </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B45" s="18"/>
-      <c r="C45" s="19">
-        <f>+C43+C34</f>
-        <v>2336792.1170000001</v>
-      </c>
+      <c r="A45" s="214" t="s">
+        <v>134</v>
+      </c>
+      <c r="B45" s="215"/>
+      <c r="C45" s="215"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="215"/>
+      <c r="B46" s="215"/>
+      <c r="C46" s="215"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="233" t="s">
-        <v>138</v>
-      </c>
-      <c r="B47" s="234"/>
-      <c r="C47" s="234"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="234"/>
-      <c r="B48" s="234"/>
-      <c r="C48" s="234"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="234"/>
-      <c r="B49" s="234"/>
-      <c r="C49" s="234"/>
-    </row>
-    <row r="50" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="234"/>
-      <c r="B50" s="234"/>
-      <c r="C50" s="234"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-    </row>
-    <row r="51" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="4"/>
-      <c r="C51" s="159"/>
+      <c r="A47" s="215"/>
+      <c r="B47" s="215"/>
+      <c r="C47" s="215"/>
+    </row>
+    <row r="48" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="215"/>
+      <c r="B48" s="215"/>
+      <c r="C48" s="215"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+    </row>
+    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="4"/>
+      <c r="C49" s="157"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="226" t="s">
+        <v>117</v>
+      </c>
+      <c r="B50" s="28"/>
+      <c r="C50" s="227">
+        <v>629534.61</v>
+      </c>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="226" t="s">
+        <v>131</v>
+      </c>
+      <c r="B51" s="28"/>
+      <c r="C51" s="31">
+        <f>-(C32-C30)</f>
+        <v>-1629792.1170000001</v>
+      </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
     </row>
-    <row r="52" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="160" t="s">
-        <v>117</v>
-      </c>
-      <c r="B52" s="158"/>
-      <c r="C52" s="161">
-        <v>-135380.74219829985</v>
-      </c>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-    </row>
-    <row r="53" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="160" t="s">
-        <v>132</v>
-      </c>
-      <c r="B53" s="158"/>
-      <c r="C53" s="163">
-        <f>-(C34-C32)</f>
-        <v>-2336792.1170000001</v>
-      </c>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-    </row>
-    <row r="54" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="160" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="226" t="s">
         <v>113</v>
       </c>
-      <c r="B54" s="158"/>
-      <c r="C54" s="184">
+      <c r="B52" s="28"/>
+      <c r="C52" s="228">
         <f>'prorrateo '!F31</f>
-        <v>2388252.0715338252</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="164"/>
-      <c r="C55" s="165"/>
-    </row>
-    <row r="56" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="162" t="s">
+        <v>2538562.2581728254</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="226" t="s">
+        <v>138</v>
+      </c>
+      <c r="B53" s="28"/>
+      <c r="C53" s="229">
+        <v>-307000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="226" t="s">
+        <v>137</v>
+      </c>
+      <c r="B54" s="28"/>
+      <c r="C54" s="229">
+        <v>-400000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="226" t="s">
         <v>8</v>
       </c>
-      <c r="B56" s="157"/>
-      <c r="C56" s="166">
-        <f>SUM(C50:C54)</f>
-        <v>-83920.787664474919</v>
-      </c>
-      <c r="D56" s="5"/>
-    </row>
-    <row r="57" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="9"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="10"/>
-    </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="195"/>
-      <c r="B58" s="195"/>
-      <c r="C58" s="195"/>
-      <c r="F58" s="44"/>
-    </row>
-    <row r="59" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="196"/>
-      <c r="B59" s="196"/>
-      <c r="C59" s="196"/>
-    </row>
-    <row r="60" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="26" t="s">
+      <c r="B55" s="28"/>
+      <c r="C55" s="227">
+        <f>SUM(C48:C54)</f>
+        <v>831304.75117282523</v>
+      </c>
+      <c r="D55" s="5"/>
+    </row>
+    <row r="56" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="9"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="10"/>
+    </row>
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="210"/>
+      <c r="B57" s="210"/>
+      <c r="C57" s="210"/>
+      <c r="F57" s="44"/>
+    </row>
+    <row r="58" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="211"/>
+      <c r="B58" s="211"/>
+      <c r="C58" s="211"/>
+    </row>
+    <row r="59" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B60" s="27"/>
-      <c r="C60" s="29"/>
+      <c r="B59" s="27"/>
+      <c r="C59" s="29"/>
+    </row>
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B60" s="28"/>
+      <c r="C60" s="31">
+        <f>-C41</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="28" t="s">
-        <v>24</v>
-      </c>
+      <c r="A61" s="28"/>
       <c r="B61" s="28"/>
-      <c r="C61" s="31">
-        <f>-C43</f>
-        <v>0</v>
-      </c>
+      <c r="C61" s="31"/>
     </row>
     <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="28"/>
       <c r="B62" s="28"/>
-      <c r="C62" s="31"/>
+      <c r="C62" s="32"/>
     </row>
     <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="28"/>
-      <c r="B63" s="28"/>
-      <c r="C63" s="32"/>
-    </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="167" t="s">
-        <v>0</v>
-      </c>
-      <c r="B64" s="168"/>
-      <c r="C64" s="169">
-        <f>SUM(C60:C63)</f>
-        <v>0</v>
-      </c>
+      <c r="A63" s="158" t="s">
+        <v>0</v>
+      </c>
+      <c r="B63" s="159"/>
+      <c r="C63" s="160">
+        <f>SUM(C59:C62)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="212" t="s">
+        <v>127</v>
+      </c>
+      <c r="B64" s="213"/>
+      <c r="C64" s="213"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="197" t="s">
-        <v>128</v>
-      </c>
-      <c r="B65" s="198"/>
-      <c r="C65" s="198"/>
+      <c r="A65" s="213"/>
+      <c r="B65" s="213"/>
+      <c r="C65" s="213"/>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="198"/>
-      <c r="B66" s="198"/>
-      <c r="C66" s="198"/>
+      <c r="A66" s="213"/>
+      <c r="B66" s="213"/>
+      <c r="C66" s="213"/>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="198"/>
-      <c r="B67" s="198"/>
-      <c r="C67" s="198"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="8"/>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
+      <c r="A67" s="8"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A58:C59"/>
-    <mergeCell ref="A65:C67"/>
-    <mergeCell ref="A47:C50"/>
+    <mergeCell ref="A57:C58"/>
+    <mergeCell ref="A64:C66"/>
+    <mergeCell ref="A45:C48"/>
   </mergeCells>
-  <phoneticPr fontId="31" type="noConversion"/>
+  <phoneticPr fontId="30" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.19685039370078741" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="91" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="89" orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
@@ -2492,23 +2379,21 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B1" s="199">
+        <v>120</v>
+      </c>
+      <c r="B1" s="216">
         <f>D1</f>
-        <v>1436145.71</v>
-      </c>
-      <c r="C1" s="199"/>
+        <v>1929792.1170000001</v>
+      </c>
+      <c r="C1" s="216"/>
       <c r="D1" s="141">
-        <v>1436145.71</v>
+        <v>1929792.1170000001</v>
       </c>
       <c r="E1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G1" s="200">
-        <v>1000000</v>
-      </c>
-      <c r="H1" s="200"/>
+        <v>119</v>
+      </c>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
     </row>
     <row r="2" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
@@ -2532,14 +2417,14 @@
       <c r="G2" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="49" t="s">
+      <c r="H2" s="224" t="s">
         <v>109</v>
       </c>
       <c r="I2" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="J2" s="50" t="s">
         <v>122</v>
-      </c>
-      <c r="J2" s="50" t="s">
-        <v>123</v>
       </c>
       <c r="K2" s="50" t="s">
         <v>17</v>
@@ -2564,7 +2449,7 @@
       <c r="E3" s="131">
         <v>124487.04578100001</v>
       </c>
-      <c r="F3" s="231">
+      <c r="F3" s="177">
         <f>E3</f>
         <v>124487.04578100001</v>
       </c>
@@ -2578,16 +2463,16 @@
       </c>
       <c r="I3" s="56">
         <f>B$1*D3/100</f>
-        <v>73387.045781000008</v>
+        <v>98612.377178700001</v>
       </c>
       <c r="J3" s="56">
         <f>G$1*D3/100</f>
-        <v>51100</v>
+        <v>0</v>
       </c>
       <c r="K3" s="56"/>
       <c r="L3" s="57">
         <f>I3+G3+K3+J3+H3</f>
-        <v>124487.04578100001</v>
+        <v>98612.377178700001</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -2606,7 +2491,7 @@
       <c r="E4" s="131">
         <v>123999.816639</v>
       </c>
-      <c r="F4" s="231">
+      <c r="F4" s="177">
         <f t="shared" ref="F4:F18" si="0">E4</f>
         <v>123999.816639</v>
       </c>
@@ -2620,16 +2505,16 @@
       </c>
       <c r="I4" s="56">
         <f t="shared" ref="I4:I29" si="3">B$1*D4/100</f>
-        <v>73099.816638999997</v>
+        <v>98226.418755300008</v>
       </c>
       <c r="J4" s="56">
         <f t="shared" ref="J4:J29" si="4">G$1*D4/100</f>
-        <v>50900</v>
+        <v>0</v>
       </c>
       <c r="K4" s="56"/>
       <c r="L4" s="57">
         <f t="shared" ref="L4:L29" si="5">I4+G4+K4+J4+H4</f>
-        <v>123999.816639</v>
+        <v>98226.418755300008</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -2648,7 +2533,7 @@
       <c r="E5" s="131">
         <v>241472.783784</v>
       </c>
-      <c r="F5" s="231">
+      <c r="F5" s="177">
         <f>E5-141155.37</f>
         <v>100317.413784</v>
       </c>
@@ -2662,16 +2547,16 @@
       </c>
       <c r="I5" s="56">
         <f t="shared" si="3"/>
-        <v>72381.743783999991</v>
+        <v>97261.522696800006</v>
       </c>
       <c r="J5" s="56">
         <f t="shared" si="4"/>
-        <v>50400</v>
+        <v>0</v>
       </c>
       <c r="K5" s="56"/>
       <c r="L5" s="57">
         <f t="shared" si="5"/>
-        <v>269583.328584</v>
+        <v>244063.10749679999</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -2688,7 +2573,7 @@
       <c r="E6" s="131">
         <v>126923.19149100001</v>
       </c>
-      <c r="F6" s="231">
+      <c r="F6" s="177">
         <f>E6</f>
         <v>126923.19149100001</v>
       </c>
@@ -2702,18 +2587,18 @@
       </c>
       <c r="I6" s="56">
         <f t="shared" si="3"/>
-        <v>74823.191491000005</v>
+        <v>100542.16929570001</v>
       </c>
       <c r="J6" s="56">
         <f t="shared" si="4"/>
-        <v>52100</v>
+        <v>0</v>
       </c>
       <c r="K6" s="56"/>
       <c r="L6" s="57">
         <f t="shared" si="5"/>
-        <v>126923.19149100001</v>
-      </c>
-      <c r="O6" s="192"/>
+        <v>100542.16929570001</v>
+      </c>
+      <c r="O6" s="182"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="58" t="s">
@@ -2731,7 +2616,7 @@
       <c r="E7" s="131">
         <v>124487.04578100001</v>
       </c>
-      <c r="F7" s="231">
+      <c r="F7" s="177">
         <f>E7</f>
         <v>124487.04578100001</v>
       </c>
@@ -2745,18 +2630,18 @@
       </c>
       <c r="I7" s="56">
         <f t="shared" si="3"/>
-        <v>73387.045781000008</v>
+        <v>98612.377178700001</v>
       </c>
       <c r="J7" s="56">
         <f t="shared" si="4"/>
-        <v>51100</v>
+        <v>0</v>
       </c>
       <c r="K7" s="56"/>
       <c r="L7" s="57">
         <f t="shared" si="5"/>
-        <v>124487.04578100001</v>
-      </c>
-      <c r="O7" s="192"/>
+        <v>98612.377178700001</v>
+      </c>
+      <c r="O7" s="182"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
@@ -2772,7 +2657,7 @@
       <c r="E8" s="131">
         <v>123999.816639</v>
       </c>
-      <c r="F8" s="231">
+      <c r="F8" s="177">
         <f>E8</f>
         <v>123999.816639</v>
       </c>
@@ -2786,16 +2671,16 @@
       </c>
       <c r="I8" s="56">
         <f t="shared" si="3"/>
-        <v>73099.816638999997</v>
+        <v>98226.418755300008</v>
       </c>
       <c r="J8" s="56">
         <f t="shared" si="4"/>
-        <v>50900</v>
+        <v>0</v>
       </c>
       <c r="K8" s="56"/>
       <c r="L8" s="57">
         <f t="shared" si="5"/>
-        <v>123999.816639</v>
+        <v>98226.418755300008</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -2812,7 +2697,7 @@
       <c r="E9" s="131">
         <v>124487.04578100001</v>
       </c>
-      <c r="F9" s="231">
+      <c r="F9" s="177">
         <f t="shared" si="0"/>
         <v>124487.04578100001</v>
       </c>
@@ -2826,53 +2711,56 @@
       </c>
       <c r="I9" s="56">
         <f t="shared" si="3"/>
-        <v>73387.045781000008</v>
+        <v>98612.377178700001</v>
       </c>
       <c r="J9" s="56">
         <f t="shared" si="4"/>
-        <v>51100</v>
+        <v>0</v>
       </c>
       <c r="K9" s="56"/>
       <c r="L9" s="57">
         <f t="shared" si="5"/>
-        <v>124487.04578100001</v>
-      </c>
-      <c r="O9" s="192"/>
+        <v>98612.377178700001</v>
+      </c>
+      <c r="O9" s="182"/>
     </row>
     <row r="10" spans="1:15" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="208" t="s">
+      <c r="A10" s="185" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="209" t="s">
+      <c r="B10" s="186" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="210" t="s">
+      <c r="C10" s="187" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="211">
+      <c r="D10" s="188">
         <v>5.09</v>
       </c>
-      <c r="E10" s="212">
-        <v>769966.0654390722</v>
-      </c>
-      <c r="F10" s="213"/>
-      <c r="G10" s="214">
+      <c r="E10" s="189">
+        <v>123999.816639</v>
+      </c>
+      <c r="F10" s="190">
+        <f>E10</f>
+        <v>123999.816639</v>
+      </c>
+      <c r="G10" s="191">
         <f t="shared" si="1"/>
-        <v>769966.0654390722</v>
-      </c>
-      <c r="H10" s="214"/>
-      <c r="I10" s="214">
+        <v>0</v>
+      </c>
+      <c r="H10" s="191"/>
+      <c r="I10" s="191">
         <f t="shared" si="3"/>
-        <v>73099.816638999997</v>
-      </c>
-      <c r="J10" s="214">
+        <v>98226.418755300008</v>
+      </c>
+      <c r="J10" s="191">
         <f t="shared" si="4"/>
-        <v>50900</v>
-      </c>
-      <c r="K10" s="214"/>
-      <c r="L10" s="215">
+        <v>0</v>
+      </c>
+      <c r="K10" s="191"/>
+      <c r="L10" s="192">
         <f t="shared" si="5"/>
-        <v>893965.88207807217</v>
+        <v>98226.418755300008</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -2889,7 +2777,7 @@
       <c r="E11" s="131">
         <v>122781.74378399999</v>
       </c>
-      <c r="F11" s="231">
+      <c r="F11" s="177">
         <f>E11</f>
         <v>122781.74378399999</v>
       </c>
@@ -2903,16 +2791,16 @@
       </c>
       <c r="I11" s="56">
         <f t="shared" si="3"/>
-        <v>72381.743783999991</v>
+        <v>97261.522696800006</v>
       </c>
       <c r="J11" s="56">
         <f t="shared" si="4"/>
-        <v>50400</v>
+        <v>0</v>
       </c>
       <c r="K11" s="56"/>
       <c r="L11" s="57">
         <f t="shared" si="5"/>
-        <v>122781.74378399999</v>
+        <v>97261.522696800006</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -2929,7 +2817,7 @@
       <c r="E12" s="131">
         <v>126923.19149100001</v>
       </c>
-      <c r="F12" s="231">
+      <c r="F12" s="177">
         <f t="shared" si="0"/>
         <v>126923.19149100001</v>
       </c>
@@ -2943,16 +2831,16 @@
       </c>
       <c r="I12" s="56">
         <f t="shared" si="3"/>
-        <v>74823.191491000005</v>
+        <v>100542.16929570001</v>
       </c>
       <c r="J12" s="56">
         <f t="shared" si="4"/>
-        <v>52100</v>
+        <v>0</v>
       </c>
       <c r="K12" s="56"/>
       <c r="L12" s="57">
         <f t="shared" si="5"/>
-        <v>126923.19149100001</v>
+        <v>100542.16929570001</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -2971,7 +2859,7 @@
       <c r="E13" s="131">
         <v>124487.04578100001</v>
       </c>
-      <c r="F13" s="231">
+      <c r="F13" s="177">
         <f t="shared" si="0"/>
         <v>124487.04578100001</v>
       </c>
@@ -2985,35 +2873,35 @@
       </c>
       <c r="I13" s="56">
         <f t="shared" si="3"/>
-        <v>73387.045781000008</v>
+        <v>98612.377178700001</v>
       </c>
       <c r="J13" s="56">
         <f t="shared" si="4"/>
-        <v>51100</v>
+        <v>0</v>
       </c>
       <c r="K13" s="56"/>
       <c r="L13" s="57">
         <f t="shared" si="5"/>
-        <v>124487.04578100001</v>
+        <v>98612.377178700001</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="235" t="s">
-        <v>125</v>
+      <c r="B14" s="208" t="s">
+        <v>124</v>
       </c>
       <c r="C14" s="65" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="206">
+      <c r="D14" s="183">
         <v>5.09</v>
       </c>
       <c r="E14" s="131">
         <v>374456.40098510444</v>
       </c>
-      <c r="F14" s="231">
+      <c r="F14" s="177">
         <f>E14</f>
         <v>374456.40098510444</v>
       </c>
@@ -3027,16 +2915,16 @@
       </c>
       <c r="I14" s="66">
         <f t="shared" si="3"/>
-        <v>73099.816638999997</v>
+        <v>98226.418755300008</v>
       </c>
       <c r="J14" s="66">
         <f t="shared" si="4"/>
-        <v>50900</v>
+        <v>0</v>
       </c>
       <c r="K14" s="66"/>
-      <c r="L14" s="207">
+      <c r="L14" s="184">
         <f t="shared" si="5"/>
-        <v>123999.816639</v>
+        <v>98226.418755300008</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -3055,7 +2943,7 @@
       <c r="E15" s="131">
         <v>383275.49139613437</v>
       </c>
-      <c r="F15" s="187"/>
+      <c r="F15" s="177"/>
       <c r="G15" s="56">
         <f t="shared" si="1"/>
         <v>383275.49139613437</v>
@@ -3066,16 +2954,16 @@
       </c>
       <c r="I15" s="56">
         <f t="shared" si="3"/>
-        <v>72381.743783999991</v>
+        <v>97261.522696800006</v>
       </c>
       <c r="J15" s="56">
         <f t="shared" si="4"/>
-        <v>50400</v>
+        <v>0</v>
       </c>
       <c r="K15" s="56"/>
       <c r="L15" s="57">
         <f t="shared" si="5"/>
-        <v>521388.25483597972</v>
+        <v>495868.03374877974</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -3094,7 +2982,7 @@
       <c r="E16" s="131">
         <v>126923.19149100001</v>
       </c>
-      <c r="F16" s="231">
+      <c r="F16" s="177">
         <f>E16</f>
         <v>126923.19149100001</v>
       </c>
@@ -3108,16 +2996,16 @@
       </c>
       <c r="I16" s="56">
         <f t="shared" si="3"/>
-        <v>74823.191491000005</v>
+        <v>100542.16929570001</v>
       </c>
       <c r="J16" s="56">
         <f t="shared" si="4"/>
-        <v>52100</v>
+        <v>0</v>
       </c>
       <c r="K16" s="56"/>
       <c r="L16" s="57">
         <f t="shared" si="5"/>
-        <v>126923.19149100001</v>
+        <v>100542.16929570001</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -3134,7 +3022,7 @@
       <c r="E17" s="131">
         <v>122781.74378399999</v>
       </c>
-      <c r="F17" s="231">
+      <c r="F17" s="177">
         <f t="shared" si="0"/>
         <v>122781.74378399999</v>
       </c>
@@ -3148,16 +3036,16 @@
       </c>
       <c r="I17" s="56">
         <f t="shared" si="3"/>
-        <v>72381.743783999991</v>
+        <v>97261.522696800006</v>
       </c>
       <c r="J17" s="56">
         <f t="shared" si="4"/>
-        <v>50400</v>
+        <v>0</v>
       </c>
       <c r="K17" s="56"/>
       <c r="L17" s="57">
         <f t="shared" si="5"/>
-        <v>122781.74378399999</v>
+        <v>97261.522696800006</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3174,7 +3062,7 @@
       <c r="E18" s="131">
         <v>126923.19149100001</v>
       </c>
-      <c r="F18" s="231">
+      <c r="F18" s="177">
         <f t="shared" si="0"/>
         <v>126923.19149100001</v>
       </c>
@@ -3188,16 +3076,16 @@
       </c>
       <c r="I18" s="56">
         <f t="shared" si="3"/>
-        <v>74823.191491000005</v>
+        <v>100542.16929570001</v>
       </c>
       <c r="J18" s="56">
         <f t="shared" si="4"/>
-        <v>52100</v>
+        <v>0</v>
       </c>
       <c r="K18" s="56"/>
       <c r="L18" s="57">
         <f t="shared" si="5"/>
-        <v>126923.19149100001</v>
+        <v>100542.16929570001</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -3214,7 +3102,7 @@
       <c r="E19" s="131">
         <v>180274.78253999999</v>
       </c>
-      <c r="F19" s="231">
+      <c r="F19" s="177">
         <f>E19</f>
         <v>180274.78253999999</v>
       </c>
@@ -3228,52 +3116,53 @@
       </c>
       <c r="I19" s="56">
         <f t="shared" si="3"/>
-        <v>106274.78254</v>
+        <v>142804.61665800001</v>
       </c>
       <c r="J19" s="56">
         <f t="shared" si="4"/>
-        <v>74000</v>
+        <v>0</v>
       </c>
       <c r="K19" s="56"/>
       <c r="L19" s="57">
         <f t="shared" si="5"/>
-        <v>180274.78253999999</v>
+        <v>142804.61665800001</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="24" x14ac:dyDescent="0.25">
-      <c r="A20" s="216"/>
-      <c r="B20" s="209" t="s">
+      <c r="A20" s="193"/>
+      <c r="B20" s="186" t="s">
         <v>116</v>
       </c>
-      <c r="C20" s="210" t="s">
+      <c r="C20" s="187" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="211">
+      <c r="D20" s="188">
         <v>1.08</v>
       </c>
-      <c r="E20" s="212">
-        <v>163371.97459218031</v>
-      </c>
-      <c r="F20" s="213">
-        <v>0</v>
-      </c>
-      <c r="G20" s="214">
+      <c r="E20" s="189">
+        <v>26310.37</v>
+      </c>
+      <c r="F20" s="190">
+        <f>E20</f>
+        <v>26310.37</v>
+      </c>
+      <c r="G20" s="191">
         <f t="shared" si="1"/>
-        <v>163371.97459218031</v>
-      </c>
-      <c r="H20" s="214"/>
-      <c r="I20" s="214">
+        <v>0</v>
+      </c>
+      <c r="H20" s="191"/>
+      <c r="I20" s="191">
         <f t="shared" si="3"/>
-        <v>15510.373668</v>
-      </c>
-      <c r="J20" s="214">
+        <v>20841.754863600003</v>
+      </c>
+      <c r="J20" s="191">
         <f t="shared" si="4"/>
-        <v>10800</v>
-      </c>
-      <c r="K20" s="214"/>
-      <c r="L20" s="215">
+        <v>0</v>
+      </c>
+      <c r="K20" s="191"/>
+      <c r="L20" s="192">
         <f t="shared" si="5"/>
-        <v>189682.34826018033</v>
+        <v>20841.754863600003</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -3290,7 +3179,7 @@
       <c r="E21" s="131">
         <v>26310.373668</v>
       </c>
-      <c r="F21" s="231">
+      <c r="F21" s="177">
         <f>E21</f>
         <v>26310.373668</v>
       </c>
@@ -3304,16 +3193,16 @@
       </c>
       <c r="I21" s="56">
         <f t="shared" si="3"/>
-        <v>15510.373668</v>
+        <v>20841.754863600003</v>
       </c>
       <c r="J21" s="56">
         <f t="shared" si="4"/>
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="K21" s="66"/>
       <c r="L21" s="57">
         <f t="shared" si="5"/>
-        <v>26310.373668</v>
+        <v>20841.754863600003</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -3328,7 +3217,7 @@
       <c r="E22" s="146">
         <v>163371.97459218031</v>
       </c>
-      <c r="F22" s="191">
+      <c r="F22" s="181">
         <v>0</v>
       </c>
       <c r="G22" s="147">
@@ -3341,16 +3230,16 @@
       </c>
       <c r="I22" s="147">
         <f t="shared" si="3"/>
-        <v>15510.373668</v>
+        <v>20841.754863600003</v>
       </c>
       <c r="J22" s="147">
         <f t="shared" si="4"/>
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="K22" s="147"/>
       <c r="L22" s="148">
         <f t="shared" si="5"/>
-        <v>196217.22724386753</v>
+        <v>190748.60843946753</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -3367,7 +3256,7 @@
       <c r="E23" s="131">
         <v>48774.373668</v>
       </c>
-      <c r="F23" s="231">
+      <c r="F23" s="177">
         <f>E23</f>
         <v>48774.373668</v>
       </c>
@@ -3381,16 +3270,16 @@
       </c>
       <c r="I23" s="56">
         <f t="shared" si="3"/>
-        <v>15510.373668</v>
+        <v>20841.754863600003</v>
       </c>
       <c r="J23" s="56">
         <f t="shared" si="4"/>
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="K23" s="56"/>
       <c r="L23" s="57">
         <f t="shared" si="5"/>
-        <v>26310.373668</v>
+        <v>20841.754863600003</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -3409,7 +3298,7 @@
       <c r="E24" s="131">
         <v>26310.373668</v>
       </c>
-      <c r="F24" s="231">
+      <c r="F24" s="177">
         <f t="shared" ref="F24" si="6">E24</f>
         <v>26310.373668</v>
       </c>
@@ -3423,16 +3312,16 @@
       </c>
       <c r="I24" s="56">
         <f t="shared" si="3"/>
-        <v>15510.373668</v>
+        <v>20841.754863600003</v>
       </c>
       <c r="J24" s="56">
         <f t="shared" si="4"/>
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="K24" s="56"/>
       <c r="L24" s="57">
         <f t="shared" si="5"/>
-        <v>26310.373668</v>
+        <v>20841.754863600003</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -3449,7 +3338,7 @@
       <c r="E25" s="131">
         <v>53673.162282719997</v>
       </c>
-      <c r="F25" s="231">
+      <c r="F25" s="177">
         <f>E25</f>
         <v>53673.162282719997</v>
       </c>
@@ -3463,16 +3352,16 @@
       </c>
       <c r="I25" s="56">
         <f t="shared" si="3"/>
-        <v>15510.373668</v>
+        <v>20841.754863600003</v>
       </c>
       <c r="J25" s="56">
         <f t="shared" si="4"/>
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="K25" s="56"/>
       <c r="L25" s="57">
         <f t="shared" si="5"/>
-        <v>26310.373668</v>
+        <v>20841.754863600003</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -3489,7 +3378,7 @@
       <c r="E26" s="131">
         <v>26310.373668</v>
       </c>
-      <c r="F26" s="231">
+      <c r="F26" s="177">
         <f t="shared" ref="F26:F28" si="7">E26</f>
         <v>26310.373668</v>
       </c>
@@ -3503,16 +3392,16 @@
       </c>
       <c r="I26" s="56">
         <f t="shared" si="3"/>
-        <v>15510.373668</v>
+        <v>20841.754863600003</v>
       </c>
       <c r="J26" s="56">
         <f t="shared" si="4"/>
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="K26" s="56"/>
       <c r="L26" s="57">
         <f t="shared" si="5"/>
-        <v>26310.373668</v>
+        <v>20841.754863600003</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -3529,7 +3418,7 @@
       <c r="E27" s="131">
         <v>26310.373668</v>
       </c>
-      <c r="F27" s="231">
+      <c r="F27" s="177">
         <f t="shared" si="7"/>
         <v>26310.373668</v>
       </c>
@@ -3543,16 +3432,16 @@
       </c>
       <c r="I27" s="56">
         <f t="shared" si="3"/>
-        <v>15510.373668</v>
+        <v>20841.754863600003</v>
       </c>
       <c r="J27" s="56">
         <f t="shared" si="4"/>
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="K27" s="56"/>
       <c r="L27" s="57">
         <f t="shared" si="5"/>
-        <v>26310.373668</v>
+        <v>20841.754863600003</v>
       </c>
       <c r="O27" s="44">
         <f>F27+F26+F19</f>
@@ -3574,7 +3463,7 @@
       <c r="E28" s="131">
         <v>26310.373668</v>
       </c>
-      <c r="F28" s="231">
+      <c r="F28" s="177">
         <f t="shared" si="7"/>
         <v>26310.373668</v>
       </c>
@@ -3588,16 +3477,16 @@
       </c>
       <c r="I28" s="56">
         <f t="shared" si="3"/>
-        <v>15510.373668</v>
+        <v>20841.754863600003</v>
       </c>
       <c r="J28" s="56">
         <f t="shared" si="4"/>
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="K28" s="56"/>
       <c r="L28" s="57">
         <f t="shared" si="5"/>
-        <v>26310.373668</v>
+        <v>20841.754863600003</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3616,7 +3505,7 @@
       <c r="E29" s="131">
         <v>82130.462442028787</v>
       </c>
-      <c r="F29" s="187"/>
+      <c r="F29" s="177"/>
       <c r="G29" s="56">
         <f t="shared" si="1"/>
         <v>82130.462442028787</v>
@@ -3627,16 +3516,16 @@
       </c>
       <c r="I29" s="56">
         <f t="shared" si="3"/>
-        <v>15510.373668</v>
+        <v>20841.754863600003</v>
       </c>
       <c r="J29" s="56">
         <f t="shared" si="4"/>
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="K29" s="56"/>
       <c r="L29" s="57">
         <f t="shared" si="5"/>
-        <v>111726.05460770994</v>
+        <v>106257.43580330994</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -3666,84 +3555,84 @@
       <c r="E31" s="75"/>
       <c r="F31" s="137">
         <f>SUM(F3:F30)</f>
-        <v>2388252.0715338252</v>
+        <v>2538562.2581728254</v>
       </c>
       <c r="G31" s="77"/>
       <c r="H31" s="77"/>
       <c r="I31" s="138">
         <f>SUM(I3:I30)</f>
-        <v>1436145.7100000009</v>
+        <v>1929792.1170000006</v>
       </c>
       <c r="J31" s="138">
         <f>SUM(J3:J30)</f>
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="K31" s="137"/>
       <c r="L31" s="137">
         <f>SUM(L3:L29)</f>
-        <v>4170214.3803988108</v>
+        <v>2730522.7473675553</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J32" s="22"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="232" t="s">
-        <v>137</v>
-      </c>
-      <c r="B33" s="232"/>
-      <c r="C33" s="232"/>
-      <c r="D33" s="232"/>
-      <c r="E33" s="232"/>
-      <c r="F33" s="232"/>
-      <c r="G33" s="232"/>
-      <c r="H33" s="232"/>
-      <c r="I33" s="232"/>
-      <c r="J33" s="232"/>
-      <c r="K33" s="232"/>
-      <c r="L33" s="232"/>
+      <c r="A33" s="225" t="s">
+        <v>136</v>
+      </c>
+      <c r="B33" s="225"/>
+      <c r="C33" s="225"/>
+      <c r="D33" s="225"/>
+      <c r="E33" s="225"/>
+      <c r="F33" s="225"/>
+      <c r="G33" s="225"/>
+      <c r="H33" s="225"/>
+      <c r="I33" s="225"/>
+      <c r="J33" s="225"/>
+      <c r="K33" s="225"/>
+      <c r="L33" s="225"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="232"/>
-      <c r="B34" s="232"/>
-      <c r="C34" s="232"/>
-      <c r="D34" s="232"/>
-      <c r="E34" s="232"/>
-      <c r="F34" s="232"/>
-      <c r="G34" s="232"/>
-      <c r="H34" s="232"/>
-      <c r="I34" s="232"/>
-      <c r="J34" s="232"/>
-      <c r="K34" s="232"/>
-      <c r="L34" s="232"/>
+      <c r="A34" s="225"/>
+      <c r="B34" s="225"/>
+      <c r="C34" s="225"/>
+      <c r="D34" s="225"/>
+      <c r="E34" s="225"/>
+      <c r="F34" s="225"/>
+      <c r="G34" s="225"/>
+      <c r="H34" s="225"/>
+      <c r="I34" s="225"/>
+      <c r="J34" s="225"/>
+      <c r="K34" s="225"/>
+      <c r="L34" s="225"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="232"/>
-      <c r="B35" s="232"/>
-      <c r="C35" s="232"/>
-      <c r="D35" s="232"/>
-      <c r="E35" s="232"/>
-      <c r="F35" s="232"/>
-      <c r="G35" s="232"/>
-      <c r="H35" s="232"/>
-      <c r="I35" s="232"/>
-      <c r="J35" s="232"/>
-      <c r="K35" s="232"/>
-      <c r="L35" s="232"/>
+      <c r="A35" s="225"/>
+      <c r="B35" s="225"/>
+      <c r="C35" s="225"/>
+      <c r="D35" s="225"/>
+      <c r="E35" s="225"/>
+      <c r="F35" s="225"/>
+      <c r="G35" s="225"/>
+      <c r="H35" s="225"/>
+      <c r="I35" s="225"/>
+      <c r="J35" s="225"/>
+      <c r="K35" s="225"/>
+      <c r="L35" s="225"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="232"/>
-      <c r="B36" s="232"/>
-      <c r="C36" s="232"/>
-      <c r="D36" s="232"/>
-      <c r="E36" s="232"/>
-      <c r="F36" s="232"/>
-      <c r="G36" s="232"/>
-      <c r="H36" s="232"/>
-      <c r="I36" s="232"/>
-      <c r="J36" s="232"/>
-      <c r="K36" s="232"/>
-      <c r="L36" s="232"/>
+      <c r="A36" s="225"/>
+      <c r="B36" s="225"/>
+      <c r="C36" s="225"/>
+      <c r="D36" s="225"/>
+      <c r="E36" s="225"/>
+      <c r="F36" s="225"/>
+      <c r="G36" s="225"/>
+      <c r="H36" s="225"/>
+      <c r="I36" s="225"/>
+      <c r="J36" s="225"/>
+      <c r="K36" s="225"/>
+      <c r="L36" s="225"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E40" s="21"/>
@@ -3783,113 +3672,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="201" t="s">
+      <c r="A1" s="218" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="202"/>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="202"/>
-      <c r="H1" s="202"/>
-      <c r="I1" s="202"/>
-      <c r="J1" s="202"/>
-      <c r="K1" s="202"/>
-      <c r="L1" s="202"/>
-      <c r="M1" s="202"/>
-      <c r="N1" s="203"/>
+      <c r="B1" s="219"/>
+      <c r="C1" s="219"/>
+      <c r="D1" s="219"/>
+      <c r="E1" s="219"/>
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="219"/>
+      <c r="J1" s="219"/>
+      <c r="K1" s="219"/>
+      <c r="L1" s="219"/>
+      <c r="M1" s="219"/>
+      <c r="N1" s="220"/>
       <c r="O1" s="78"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="79"/>
       <c r="B2" s="79"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="174"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
-      <c r="L2" s="173"/>
-      <c r="M2" s="173"/>
-      <c r="N2" s="173"/>
+      <c r="C2" s="164"/>
+      <c r="D2" s="164"/>
+      <c r="E2" s="164"/>
+      <c r="F2" s="164"/>
+      <c r="G2" s="164"/>
+      <c r="H2" s="165"/>
+      <c r="I2" s="164"/>
+      <c r="J2" s="164"/>
+      <c r="K2" s="164"/>
+      <c r="L2" s="164"/>
+      <c r="M2" s="164"/>
+      <c r="N2" s="164"/>
       <c r="O2" s="80"/>
       <c r="P2" s="11"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="82"/>
       <c r="B3" s="82"/>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="174"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
-      <c r="L3" s="173"/>
-      <c r="M3" s="173"/>
-      <c r="N3" s="173"/>
+      <c r="C3" s="166"/>
+      <c r="D3" s="166"/>
+      <c r="E3" s="166"/>
+      <c r="F3" s="166"/>
+      <c r="G3" s="166"/>
+      <c r="H3" s="165"/>
+      <c r="I3" s="164"/>
+      <c r="J3" s="164"/>
+      <c r="K3" s="164"/>
+      <c r="L3" s="164"/>
+      <c r="M3" s="164"/>
+      <c r="N3" s="164"/>
       <c r="O3" s="80"/>
       <c r="P3" s="11"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="82"/>
       <c r="B4" s="82"/>
-      <c r="C4" s="175"/>
-      <c r="D4" s="175"/>
-      <c r="E4" s="175"/>
-      <c r="F4" s="175"/>
-      <c r="G4" s="175"/>
-      <c r="H4" s="174"/>
-      <c r="I4" s="173" t="s">
+      <c r="C4" s="166"/>
+      <c r="D4" s="166"/>
+      <c r="E4" s="166"/>
+      <c r="F4" s="166"/>
+      <c r="G4" s="166"/>
+      <c r="H4" s="165"/>
+      <c r="I4" s="164" t="s">
         <v>78</v>
       </c>
-      <c r="J4" s="173"/>
-      <c r="K4" s="173"/>
-      <c r="L4" s="173"/>
-      <c r="M4" s="173"/>
-      <c r="N4" s="173"/>
+      <c r="J4" s="164"/>
+      <c r="K4" s="164"/>
+      <c r="L4" s="164"/>
+      <c r="M4" s="164"/>
+      <c r="N4" s="164"/>
       <c r="O4" s="80"/>
       <c r="P4" s="11"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="82"/>
       <c r="B5" s="82"/>
-      <c r="C5" s="175"/>
-      <c r="D5" s="175"/>
-      <c r="E5" s="175"/>
-      <c r="F5" s="175"/>
-      <c r="G5" s="175"/>
-      <c r="H5" s="174"/>
-      <c r="I5" s="173"/>
-      <c r="J5" s="173"/>
-      <c r="K5" s="173"/>
-      <c r="L5" s="173"/>
-      <c r="M5" s="173"/>
-      <c r="N5" s="173"/>
+      <c r="C5" s="166"/>
+      <c r="D5" s="166"/>
+      <c r="E5" s="166"/>
+      <c r="F5" s="166"/>
+      <c r="G5" s="166"/>
+      <c r="H5" s="165"/>
+      <c r="I5" s="164"/>
+      <c r="J5" s="164"/>
+      <c r="K5" s="164"/>
+      <c r="L5" s="164"/>
+      <c r="M5" s="164"/>
+      <c r="N5" s="164"/>
       <c r="O5" s="80"/>
       <c r="P5" s="11"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="82"/>
       <c r="B6" s="82"/>
-      <c r="C6" s="173"/>
+      <c r="C6" s="164"/>
       <c r="D6" s="28"/>
-      <c r="E6" s="173"/>
-      <c r="F6" s="173"/>
-      <c r="G6" s="173"/>
-      <c r="H6" s="174"/>
-      <c r="I6" s="173"/>
-      <c r="J6" s="173"/>
-      <c r="K6" s="173"/>
-      <c r="L6" s="173"/>
-      <c r="M6" s="173"/>
-      <c r="N6" s="173"/>
+      <c r="E6" s="164"/>
+      <c r="F6" s="164"/>
+      <c r="G6" s="164"/>
+      <c r="H6" s="165"/>
+      <c r="I6" s="164"/>
+      <c r="J6" s="164"/>
+      <c r="K6" s="164"/>
+      <c r="L6" s="164"/>
+      <c r="M6" s="164"/>
+      <c r="N6" s="164"/>
       <c r="O6" s="80"/>
       <c r="P6" s="11"/>
     </row>
@@ -3898,25 +3787,25 @@
       <c r="B7" s="83" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="236">
+      <c r="C7" s="209">
         <v>699182.21</v>
       </c>
       <c r="D7" s="28"/>
-      <c r="E7" s="173"/>
-      <c r="F7" s="173" t="s">
+      <c r="E7" s="164"/>
+      <c r="F7" s="164" t="s">
         <v>110</v>
       </c>
-      <c r="G7" s="173"/>
-      <c r="H7" s="174"/>
-      <c r="I7" s="173"/>
-      <c r="J7" s="173" t="str">
+      <c r="G7" s="164"/>
+      <c r="H7" s="165"/>
+      <c r="I7" s="164"/>
+      <c r="J7" s="164" t="str">
         <f>'detalle y gastos'!C7</f>
         <v>Vto. 15/09</v>
       </c>
-      <c r="K7" s="173"/>
-      <c r="L7" s="173"/>
-      <c r="M7" s="173"/>
-      <c r="N7" s="173"/>
+      <c r="K7" s="164"/>
+      <c r="L7" s="164"/>
+      <c r="M7" s="164"/>
+      <c r="N7" s="164"/>
       <c r="O7" s="80"/>
       <c r="P7" s="11"/>
     </row>
@@ -3936,11 +3825,11 @@
         <f>C8-J38</f>
         <v>-196408.73539999995</v>
       </c>
-      <c r="L8" s="205">
+      <c r="L8" s="222">
         <f>C7-J38</f>
         <v>502773.47460000002</v>
       </c>
-      <c r="M8" s="205"/>
+      <c r="M8" s="222"/>
       <c r="N8" s="86"/>
       <c r="O8" s="80"/>
       <c r="P8" s="11"/>
@@ -4042,7 +3931,7 @@
       </c>
       <c r="O10" s="99">
         <f>N10+'prorrateo '!L3</f>
-        <v>171205.81573306001</v>
+        <v>145331.14713075999</v>
       </c>
       <c r="P10" s="11"/>
     </row>
@@ -4098,7 +3987,7 @@
       </c>
       <c r="O11" s="99">
         <f>N11+'prorrateo '!L4</f>
-        <v>172174.89609614003</v>
+        <v>146401.49821244003</v>
       </c>
       <c r="P11" s="11"/>
     </row>
@@ -4154,7 +4043,7 @@
       </c>
       <c r="O12" s="99">
         <f>N12+'prorrateo '!L5</f>
-        <v>297717.96430384001</v>
+        <v>272197.74321663997</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
@@ -4168,13 +4057,13 @@
       <c r="B13" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="C13" s="176" t="s">
+      <c r="C13" s="167" t="s">
         <v>40</v>
       </c>
       <c r="D13" s="102" t="s">
         <v>93</v>
       </c>
-      <c r="E13" s="177">
+      <c r="E13" s="168">
         <v>5.21</v>
       </c>
       <c r="F13" s="105">
@@ -4187,7 +4076,7 @@
         <f t="shared" si="1"/>
         <v>77.400000000000091</v>
       </c>
-      <c r="I13" s="178">
+      <c r="I13" s="169">
         <f t="shared" si="0"/>
         <v>5.4180000000000073</v>
       </c>
@@ -4195,7 +4084,7 @@
         <f t="shared" si="2"/>
         <v>7259.1138000000092</v>
       </c>
-      <c r="K13" s="179">
+      <c r="K13" s="170">
         <f>K8*E13%</f>
         <v>-10232.895114339997</v>
       </c>
@@ -4203,7 +4092,7 @@
         <f t="shared" si="3"/>
         <v>26194.49802666</v>
       </c>
-      <c r="M13" s="180">
+      <c r="M13" s="171">
         <f t="shared" si="4"/>
         <v>77.400000000000091</v>
       </c>
@@ -4213,7 +4102,7 @@
       </c>
       <c r="O13" s="99">
         <f>N13+'prorrateo '!L6</f>
-        <v>160376.80331766</v>
+        <v>133995.78112236003</v>
       </c>
       <c r="P13" s="11"/>
     </row>
@@ -4269,7 +4158,7 @@
       </c>
       <c r="O14" s="99">
         <f>N14+'prorrateo '!L7</f>
-        <v>155993.56433306</v>
+        <v>130118.89573076001</v>
       </c>
       <c r="P14" s="11"/>
     </row>
@@ -4325,7 +4214,7 @@
       </c>
       <c r="O15" s="99">
         <f>N15+'prorrateo '!L8</f>
-        <v>159973.20739614003</v>
+        <v>134199.80951244003</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -4380,7 +4269,7 @@
       </c>
       <c r="O16" s="99">
         <f>N16+'prorrateo '!L9</f>
-        <v>157934.95523306003</v>
+        <v>132060.28663076003</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -4390,52 +4279,52 @@
       <c r="B17" s="91">
         <v>9</v>
       </c>
-      <c r="C17" s="217" t="s">
+      <c r="C17" s="194" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="218" t="s">
+      <c r="D17" s="195" t="s">
         <v>96</v>
       </c>
-      <c r="E17" s="219">
+      <c r="E17" s="196">
         <v>5.09</v>
       </c>
-      <c r="F17" s="221">
+      <c r="F17" s="198">
         <v>3290.2</v>
       </c>
-      <c r="G17" s="221">
+      <c r="G17" s="198">
         <v>3314.7</v>
       </c>
-      <c r="H17" s="222">
+      <c r="H17" s="199">
         <f t="shared" si="1"/>
         <v>24.5</v>
       </c>
-      <c r="I17" s="223">
+      <c r="I17" s="200">
         <f t="shared" si="0"/>
         <v>1.7150000000000001</v>
       </c>
-      <c r="J17" s="224">
+      <c r="J17" s="201">
         <f t="shared" si="2"/>
         <v>2297.7815000000001</v>
       </c>
-      <c r="K17" s="225">
+      <c r="K17" s="202">
         <f>K8*E17%</f>
         <v>-9997.2046318599969</v>
       </c>
-      <c r="L17" s="226">
+      <c r="L17" s="203">
         <f t="shared" si="3"/>
         <v>25591.169857140001</v>
       </c>
-      <c r="M17" s="227">
+      <c r="M17" s="204">
         <f t="shared" si="4"/>
         <v>24.5</v>
       </c>
-      <c r="N17" s="222">
+      <c r="N17" s="199">
         <f t="shared" si="5"/>
         <v>27888.951357140002</v>
       </c>
       <c r="O17" s="99">
         <f>N17+'prorrateo '!L10</f>
-        <v>921854.83343521215</v>
+        <v>126115.37011244001</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -4490,7 +4379,7 @@
       </c>
       <c r="O18" s="99">
         <f>N18+'prorrateo '!L11</f>
-        <v>156824.96050384</v>
+        <v>131304.73941664002</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4545,7 +4434,7 @@
       </c>
       <c r="O19" s="99">
         <f>N19+'prorrateo '!L12</f>
-        <v>177821.18531765998</v>
+        <v>151440.16312235995</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4600,7 +4489,7 @@
       </c>
       <c r="O20" s="99">
         <f>N20+'prorrateo '!L13</f>
-        <v>169527.02843306004</v>
+        <v>143652.35983076002</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -4655,7 +4544,7 @@
       </c>
       <c r="O21" s="99">
         <f>N21+'prorrateo '!L14</f>
-        <v>160038.85829614001</v>
+        <v>134265.46041244001</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -4710,7 +4599,7 @@
       </c>
       <c r="O22" s="99">
         <f>N22+'prorrateo '!L15</f>
-        <v>551483.03885581973</v>
+        <v>525962.81776861975</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -4765,7 +4654,7 @@
       </c>
       <c r="O23" s="99">
         <f>N23+'prorrateo '!L16</f>
-        <v>163931.33061766002</v>
+        <v>137550.30842236002</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -4820,7 +4709,7 @@
       </c>
       <c r="O24" s="99">
         <f>N24+'prorrateo '!L17</f>
-        <v>152923.42130384</v>
+        <v>127403.20021664002</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -4875,7 +4764,7 @@
       </c>
       <c r="O25" s="99">
         <f>N25+'prorrateo '!L18</f>
-        <v>160226.74411765998</v>
+        <v>133845.72192236001</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -4930,7 +4819,7 @@
       </c>
       <c r="O26" s="99">
         <f>N26+'prorrateo '!L19</f>
-        <v>243290.20206039987</v>
+        <v>205820.03617839993</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4940,41 +4829,41 @@
       <c r="B27" s="92">
         <v>19</v>
       </c>
-      <c r="C27" s="228" t="s">
+      <c r="C27" s="205" t="s">
         <v>67</v>
       </c>
-      <c r="D27" s="229" t="s">
+      <c r="D27" s="206" t="s">
         <v>98</v>
       </c>
-      <c r="E27" s="230">
+      <c r="E27" s="207">
         <v>1.08</v>
       </c>
-      <c r="F27" s="220"/>
-      <c r="G27" s="221"/>
-      <c r="H27" s="222">
+      <c r="F27" s="197"/>
+      <c r="G27" s="198"/>
+      <c r="H27" s="199">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I27" s="223">
+      <c r="I27" s="200">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J27" s="224"/>
-      <c r="K27" s="225"/>
-      <c r="L27" s="226">
+      <c r="J27" s="201"/>
+      <c r="K27" s="202"/>
+      <c r="L27" s="203">
         <f t="shared" si="3"/>
         <v>5429.9535256800009</v>
       </c>
-      <c r="M27" s="227">
-        <v>0</v>
-      </c>
-      <c r="N27" s="222">
+      <c r="M27" s="204">
+        <v>0</v>
+      </c>
+      <c r="N27" s="199">
         <f t="shared" ref="N27:N37" si="6">J27+L27</f>
         <v>5429.9535256800009</v>
       </c>
       <c r="O27" s="99">
         <f>N27+'prorrateo '!L20</f>
-        <v>195112.30178586033</v>
+        <v>26271.708389280004</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -4982,7 +4871,7 @@
         <v>20</v>
       </c>
       <c r="B28" s="92"/>
-      <c r="C28" s="181" t="s">
+      <c r="C28" s="172" t="s">
         <v>68</v>
       </c>
       <c r="D28" s="104"/>
@@ -4994,11 +4883,11 @@
       <c r="H28" s="106">
         <v>0</v>
       </c>
-      <c r="I28" s="182">
+      <c r="I28" s="173">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="183"/>
+      <c r="J28" s="174"/>
       <c r="K28" s="108"/>
       <c r="L28" s="129">
         <f t="shared" si="3"/>
@@ -5013,13 +4902,13 @@
       </c>
       <c r="O28" s="99">
         <f>N28+'prorrateo '!L21</f>
-        <v>31740.327193680001</v>
+        <v>26271.708389280004</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="100"/>
       <c r="B29" s="92"/>
-      <c r="C29" s="170" t="s">
+      <c r="C29" s="161" t="s">
         <v>69</v>
       </c>
       <c r="D29" s="149"/>
@@ -5029,8 +4918,8 @@
       <c r="F29" s="149"/>
       <c r="G29" s="149"/>
       <c r="H29" s="150"/>
-      <c r="I29" s="171"/>
-      <c r="J29" s="172"/>
+      <c r="I29" s="162"/>
+      <c r="J29" s="163"/>
       <c r="K29" s="151"/>
       <c r="L29" s="152">
         <f t="shared" si="3"/>
@@ -5045,13 +4934,13 @@
       </c>
       <c r="O29" s="99">
         <f>N29+'prorrateo '!L22</f>
-        <v>201647.18076954753</v>
+        <v>196178.56196514753</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="100"/>
       <c r="B30" s="92"/>
-      <c r="C30" s="181" t="s">
+      <c r="C30" s="172" t="s">
         <v>70</v>
       </c>
       <c r="D30" s="104"/>
@@ -5061,8 +4950,8 @@
       <c r="F30" s="104"/>
       <c r="G30" s="104"/>
       <c r="H30" s="106"/>
-      <c r="I30" s="182"/>
-      <c r="J30" s="183"/>
+      <c r="I30" s="173"/>
+      <c r="J30" s="174"/>
       <c r="K30" s="108"/>
       <c r="L30" s="129">
         <f t="shared" si="3"/>
@@ -5077,13 +4966,13 @@
       </c>
       <c r="O30" s="99">
         <f>N30+'prorrateo '!L23</f>
-        <v>31740.327193680001</v>
+        <v>26271.708389280004</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="100"/>
       <c r="B31" s="92"/>
-      <c r="C31" s="181" t="s">
+      <c r="C31" s="172" t="s">
         <v>71</v>
       </c>
       <c r="D31" s="104"/>
@@ -5093,8 +4982,8 @@
       <c r="F31" s="104"/>
       <c r="G31" s="104"/>
       <c r="H31" s="106"/>
-      <c r="I31" s="182"/>
-      <c r="J31" s="183"/>
+      <c r="I31" s="173"/>
+      <c r="J31" s="174"/>
       <c r="K31" s="108"/>
       <c r="L31" s="129">
         <f t="shared" si="3"/>
@@ -5109,7 +4998,7 @@
       </c>
       <c r="O31" s="99">
         <f>N31+'prorrateo '!L24</f>
-        <v>31740.327193680001</v>
+        <v>26271.708389280004</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -5141,7 +5030,7 @@
       </c>
       <c r="O32" s="99">
         <f>N32+'prorrateo '!L25</f>
-        <v>31740.327193680001</v>
+        <v>26271.708389280004</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -5173,7 +5062,7 @@
       </c>
       <c r="O33" s="99">
         <f>N33+'prorrateo '!L26</f>
-        <v>31740.327193680001</v>
+        <v>26271.708389280004</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -5205,7 +5094,7 @@
       </c>
       <c r="O34" s="99">
         <f>N34+'prorrateo '!L27</f>
-        <v>31740.327193680001</v>
+        <v>26271.708389280004</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -5213,7 +5102,7 @@
         <v>21</v>
       </c>
       <c r="B35" s="92"/>
-      <c r="C35" s="181" t="s">
+      <c r="C35" s="172" t="s">
         <v>75</v>
       </c>
       <c r="D35" s="104"/>
@@ -5225,11 +5114,11 @@
       <c r="H35" s="106">
         <v>0</v>
       </c>
-      <c r="I35" s="182">
+      <c r="I35" s="173">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J35" s="185"/>
+      <c r="J35" s="175"/>
       <c r="K35" s="108"/>
       <c r="L35" s="129">
         <f t="shared" si="3"/>
@@ -5244,7 +5133,7 @@
       </c>
       <c r="O35" s="99">
         <f>N35+'prorrateo '!L28</f>
-        <v>31740.327193680001</v>
+        <v>26271.708389280004</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -5252,7 +5141,7 @@
         <v>22</v>
       </c>
       <c r="B36" s="92"/>
-      <c r="C36" s="181" t="s">
+      <c r="C36" s="172" t="s">
         <v>76</v>
       </c>
       <c r="D36" s="104"/>
@@ -5264,11 +5153,11 @@
       <c r="H36" s="106">
         <v>0</v>
       </c>
-      <c r="I36" s="182">
+      <c r="I36" s="173">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J36" s="185"/>
+      <c r="J36" s="175"/>
       <c r="K36" s="108"/>
       <c r="L36" s="129">
         <f t="shared" si="3"/>
@@ -5283,7 +5172,7 @@
       </c>
       <c r="O36" s="99">
         <f>N36+'prorrateo '!L29</f>
-        <v>117156.00813338994</v>
+        <v>111687.38932898994</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -5373,18 +5262,18 @@
       <c r="A40" s="97" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="204"/>
-      <c r="D40" s="202"/>
-      <c r="E40" s="202"/>
-      <c r="F40" s="202"/>
-      <c r="G40" s="202"/>
-      <c r="H40" s="202"/>
-      <c r="I40" s="202"/>
-      <c r="J40" s="202"/>
-      <c r="K40" s="202"/>
-      <c r="L40" s="202"/>
-      <c r="M40" s="202"/>
-      <c r="N40" s="202"/>
+      <c r="C40" s="221"/>
+      <c r="D40" s="219"/>
+      <c r="E40" s="219"/>
+      <c r="F40" s="219"/>
+      <c r="G40" s="219"/>
+      <c r="H40" s="219"/>
+      <c r="I40" s="219"/>
+      <c r="J40" s="219"/>
+      <c r="K40" s="219"/>
+      <c r="L40" s="219"/>
+      <c r="M40" s="219"/>
+      <c r="N40" s="219"/>
       <c r="O40" s="97"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">

--- a/ROSALES/Agosto/expensas rosales Agosto.xlsx
+++ b/ROSALES/Agosto/expensas rosales Agosto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ROSALES\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DF8DE0-3354-44D4-97EB-043BB8634CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9016E9-5AC1-41A5-AEB7-B52625F8E2FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Edesur" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$66</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$68</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$N$40</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$L$37</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="142">
   <si>
     <t>TOTAL</t>
   </si>
@@ -446,6 +446,15 @@
   </si>
   <si>
     <t>COMPRA DE MATERIALES TECHO - OBRA TERRAZA</t>
+  </si>
+  <si>
+    <t>Servisur - reemplazo de dos lamparas de cochera y dos en terraza - Fuga y reparacion en circuito de escaleras y pallier</t>
+  </si>
+  <si>
+    <t>Casa Ruan - 6 lamparas</t>
+  </si>
+  <si>
+    <t>}</t>
   </si>
 </sst>
 </file>
@@ -1063,7 +1072,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="230">
+  <cellXfs count="234">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1388,6 +1397,16 @@
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="172" fontId="32" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1408,6 +1427,9 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="175" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1423,19 +1445,18 @@
     <xf numFmtId="164" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1853,7 +1874,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F67"/>
+  <dimension ref="A2:F69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1957,7 +1978,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="39"/>
-      <c r="C19" s="223">
+      <c r="C19" s="210">
         <v>321313.76</v>
       </c>
       <c r="D19" s="20"/>
@@ -1968,7 +1989,7 @@
         <v>133</v>
       </c>
       <c r="B20" s="39"/>
-      <c r="C20" s="223">
+      <c r="C20" s="210">
         <v>571077.30000000005</v>
       </c>
       <c r="D20" s="20"/>
@@ -2050,297 +2071,320 @@
       <c r="D27" s="45"/>
       <c r="F27" s="12"/>
     </row>
-    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="176" t="s">
-        <v>125</v>
-      </c>
-      <c r="B28" s="140"/>
+    <row r="28" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="230" t="s">
+        <v>139</v>
+      </c>
+      <c r="B28" s="231"/>
       <c r="C28" s="33">
-        <v>49940</v>
+        <v>150000</v>
       </c>
       <c r="D28" s="45"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="28" t="s">
+    <row r="29" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="232" t="s">
+        <v>140</v>
+      </c>
+      <c r="B29" s="233"/>
+      <c r="C29" s="33">
+        <v>6000</v>
+      </c>
+      <c r="D29" s="45"/>
+      <c r="F29" s="12"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="176" t="s">
+        <v>125</v>
+      </c>
+      <c r="B30" s="140"/>
+      <c r="C30" s="33">
+        <v>49940</v>
+      </c>
+      <c r="D30" s="45"/>
+      <c r="F30" s="12"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="B29" s="42"/>
-      <c r="C29" s="33">
+      <c r="B31" s="42"/>
+      <c r="C31" s="33">
         <v>45000</v>
       </c>
-      <c r="F29" s="12"/>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="28" t="s">
+      <c r="F31" s="12"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="B30" s="39"/>
-      <c r="C30" s="34">
+      <c r="B32" s="39"/>
+      <c r="C32" s="34">
         <v>300000</v>
       </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="12"/>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="40"/>
-      <c r="B31" s="41"/>
-      <c r="C31" s="23">
-        <f>SUM(C25:C30)</f>
-        <v>784691.05700000003</v>
-      </c>
-      <c r="F31" s="12"/>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="30" t="s">
+      <c r="D32" s="4"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="12"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="40"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="23">
+        <f>SUM(C25:C32)</f>
+        <v>940691.05700000003</v>
+      </c>
+      <c r="F33" s="12"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="43">
-        <f>+C31+C24</f>
-        <v>1929792.1170000001</v>
-      </c>
-      <c r="F32" s="12"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C33" s="24"/>
-      <c r="F33" s="12"/>
-    </row>
-    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="13" t="s">
+      <c r="B34" s="30"/>
+      <c r="C34" s="43">
+        <f>+C33+C24</f>
+        <v>2085792.1170000001</v>
+      </c>
+      <c r="F34" s="12"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C35" s="24"/>
+      <c r="F35" s="12"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C34" s="24"/>
-      <c r="F34" s="12"/>
-    </row>
-    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="28"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="33"/>
-      <c r="F35" s="12"/>
-    </row>
-    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="28"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="34"/>
+      <c r="C36" s="24"/>
       <c r="F36" s="12"/>
     </row>
     <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="28"/>
       <c r="B37" s="28"/>
-      <c r="C37" s="34"/>
+      <c r="C37" s="33"/>
       <c r="F37" s="12"/>
     </row>
     <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C38" s="25"/>
+      <c r="A38" s="28"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="34"/>
       <c r="F38" s="12"/>
     </row>
     <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="179" t="s">
-        <v>135</v>
-      </c>
-      <c r="B39" s="179"/>
-      <c r="C39" s="180"/>
+      <c r="A39" s="28"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="34"/>
       <c r="F39" s="12"/>
     </row>
     <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C40" s="25"/>
       <c r="F40" s="12"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="13" t="s">
+    <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="179" t="s">
+        <v>135</v>
+      </c>
+      <c r="B41" s="179"/>
+      <c r="C41" s="180"/>
+      <c r="F41" s="12"/>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C42" s="25"/>
+      <c r="F42" s="12"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="14">
-        <f>+C35+C36+C37+C40</f>
-        <v>0</v>
-      </c>
-      <c r="E41" s="6"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="18" t="s">
+      <c r="B43" s="13"/>
+      <c r="C43" s="14">
+        <f>+C37+C38+C39+C42</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="6"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B43" s="18"/>
-      <c r="C43" s="19">
-        <f>+C41+C32</f>
-        <v>1929792.1170000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="214" t="s">
+      <c r="B45" s="18"/>
+      <c r="C45" s="19">
+        <f>+C43+C34</f>
+        <v>2085792.1170000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="220" t="s">
         <v>134</v>
       </c>
-      <c r="B45" s="215"/>
-      <c r="C45" s="215"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="215"/>
-      <c r="B46" s="215"/>
-      <c r="C46" s="215"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="215"/>
-      <c r="B47" s="215"/>
-      <c r="C47" s="215"/>
-    </row>
-    <row r="48" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="215"/>
-      <c r="B48" s="215"/>
-      <c r="C48" s="215"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-    </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="4"/>
-      <c r="C49" s="157"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="226" t="s">
-        <v>117</v>
-      </c>
-      <c r="B50" s="28"/>
-      <c r="C50" s="227">
-        <v>629534.61</v>
-      </c>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="226" t="s">
-        <v>131</v>
-      </c>
-      <c r="B51" s="28"/>
-      <c r="C51" s="31">
-        <f>-(C32-C30)</f>
-        <v>-1629792.1170000001</v>
-      </c>
+      <c r="B47" s="221"/>
+      <c r="C47" s="221"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="221"/>
+      <c r="B48" s="221"/>
+      <c r="C48" s="221"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="221"/>
+      <c r="B49" s="221"/>
+      <c r="C49" s="221"/>
+    </row>
+    <row r="50" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="221"/>
+      <c r="B50" s="221"/>
+      <c r="C50" s="221"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+    </row>
+    <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="4"/>
+      <c r="C51" s="157"/>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="226" t="s">
+      <c r="A52" s="212" t="s">
+        <v>117</v>
+      </c>
+      <c r="B52" s="28"/>
+      <c r="C52" s="213">
+        <v>629534.61</v>
+      </c>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="212" t="s">
+        <v>131</v>
+      </c>
+      <c r="B53" s="28"/>
+      <c r="C53" s="31">
+        <f>-(C34-C32)</f>
+        <v>-1785792.1170000001</v>
+      </c>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="212" t="s">
         <v>113</v>
       </c>
-      <c r="B52" s="28"/>
-      <c r="C52" s="228">
+      <c r="B54" s="28"/>
+      <c r="C54" s="214">
         <f>'prorrateo '!F31</f>
         <v>2538562.2581728254</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="226" t="s">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="212" t="s">
         <v>138</v>
       </c>
-      <c r="B53" s="28"/>
-      <c r="C53" s="229">
+      <c r="B55" s="28"/>
+      <c r="C55" s="215">
         <v>-307000</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="226" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="212" t="s">
         <v>137</v>
       </c>
-      <c r="B54" s="28"/>
-      <c r="C54" s="229">
+      <c r="B56" s="28"/>
+      <c r="C56" s="215">
         <v>-400000</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="226" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="212" t="s">
         <v>8</v>
       </c>
-      <c r="B55" s="28"/>
-      <c r="C55" s="227">
-        <f>SUM(C48:C54)</f>
-        <v>831304.75117282523</v>
-      </c>
-      <c r="D55" s="5"/>
-    </row>
-    <row r="56" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="9"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="10"/>
-    </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="210"/>
-      <c r="B57" s="210"/>
-      <c r="C57" s="210"/>
-      <c r="F57" s="44"/>
-    </row>
-    <row r="58" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="211"/>
-      <c r="B58" s="211"/>
-      <c r="C58" s="211"/>
-    </row>
-    <row r="59" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="26" t="s">
+      <c r="B57" s="28"/>
+      <c r="C57" s="213">
+        <f>SUM(C50:C56)</f>
+        <v>675304.75117282523</v>
+      </c>
+      <c r="D57" s="5"/>
+    </row>
+    <row r="58" spans="1:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="9"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="10"/>
+    </row>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="216"/>
+      <c r="B59" s="216"/>
+      <c r="C59" s="216"/>
+      <c r="F59" s="44"/>
+    </row>
+    <row r="60" spans="1:6" ht="46.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="217"/>
+      <c r="B60" s="217"/>
+      <c r="C60" s="217"/>
+    </row>
+    <row r="61" spans="1:6" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B59" s="27"/>
-      <c r="C59" s="29"/>
-    </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="28" t="s">
+      <c r="B61" s="27"/>
+      <c r="C61" s="29"/>
+    </row>
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B60" s="28"/>
-      <c r="C60" s="31">
-        <f>-C41</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="28"/>
-      <c r="B61" s="28"/>
-      <c r="C61" s="31"/>
-    </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="28"/>
       <c r="B62" s="28"/>
-      <c r="C62" s="32"/>
+      <c r="C62" s="31">
+        <f>-C43</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="158" t="s">
-        <v>0</v>
-      </c>
-      <c r="B63" s="159"/>
-      <c r="C63" s="160">
-        <f>SUM(C59:C62)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="212" t="s">
+      <c r="A63" s="28"/>
+      <c r="B63" s="28"/>
+      <c r="C63" s="31"/>
+    </row>
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="28"/>
+      <c r="B64" s="28"/>
+      <c r="C64" s="32"/>
+    </row>
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="158" t="s">
+        <v>0</v>
+      </c>
+      <c r="B65" s="159"/>
+      <c r="C65" s="160">
+        <f>SUM(C61:C64)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="218" t="s">
         <v>127</v>
       </c>
-      <c r="B64" s="213"/>
-      <c r="C64" s="213"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="213"/>
-      <c r="B65" s="213"/>
-      <c r="C65" s="213"/>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="213"/>
-      <c r="B66" s="213"/>
-      <c r="C66" s="213"/>
+      <c r="B66" s="219"/>
+      <c r="C66" s="219"/>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="8"/>
-      <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
+      <c r="A67" s="219"/>
+      <c r="B67" s="219"/>
+      <c r="C67" s="219"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="219"/>
+      <c r="B68" s="219"/>
+      <c r="C68" s="219"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="8"/>
+      <c r="B69" s="8"/>
+      <c r="C69" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A57:C58"/>
-    <mergeCell ref="A64:C66"/>
-    <mergeCell ref="A45:C48"/>
+  <mergeCells count="4">
+    <mergeCell ref="A59:C60"/>
+    <mergeCell ref="A66:C68"/>
+    <mergeCell ref="A47:C50"/>
+    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <hyperlinks>
@@ -2348,7 +2392,7 @@
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.19685039370078741" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="89" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="82" orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
@@ -2381,19 +2425,19 @@
       <c r="A1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="216">
+      <c r="B1" s="222" t="str">
         <f>D1</f>
-        <v>1929792.1170000001</v>
-      </c>
-      <c r="C1" s="216"/>
-      <c r="D1" s="141">
-        <v>1929792.1170000001</v>
+        <v>}</v>
+      </c>
+      <c r="C1" s="222"/>
+      <c r="D1" s="141" t="s">
+        <v>141</v>
       </c>
       <c r="E1" t="s">
         <v>119</v>
       </c>
-      <c r="G1" s="217"/>
-      <c r="H1" s="217"/>
+      <c r="G1" s="224"/>
+      <c r="H1" s="224"/>
     </row>
     <row r="2" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="46" t="s">
@@ -2417,7 +2461,7 @@
       <c r="G2" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="224" t="s">
+      <c r="H2" s="211" t="s">
         <v>109</v>
       </c>
       <c r="I2" s="50" t="s">
@@ -2461,18 +2505,18 @@
         <f>IF(G3&gt;0,G3*4%,0)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="56">
+      <c r="I3" s="56" t="e">
         <f>B$1*D3/100</f>
-        <v>98612.377178700001</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J3" s="56">
         <f>G$1*D3/100</f>
         <v>0</v>
       </c>
       <c r="K3" s="56"/>
-      <c r="L3" s="57">
+      <c r="L3" s="57" t="e">
         <f>I3+G3+K3+J3+H3</f>
-        <v>98612.377178700001</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -2503,18 +2547,18 @@
         <f t="shared" ref="H4:H29" si="2">IF(G4&gt;0,G4*4%,0)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="56">
+      <c r="I4" s="56" t="e">
         <f t="shared" ref="I4:I29" si="3">B$1*D4/100</f>
-        <v>98226.418755300008</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J4" s="56">
         <f t="shared" ref="J4:J29" si="4">G$1*D4/100</f>
         <v>0</v>
       </c>
       <c r="K4" s="56"/>
-      <c r="L4" s="57">
+      <c r="L4" s="57" t="e">
         <f t="shared" ref="L4:L29" si="5">I4+G4+K4+J4+H4</f>
-        <v>98226.418755300008</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -2545,18 +2589,18 @@
         <f t="shared" si="2"/>
         <v>5646.2147999999997</v>
       </c>
-      <c r="I5" s="56">
+      <c r="I5" s="56" t="e">
         <f t="shared" si="3"/>
-        <v>97261.522696800006</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J5" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K5" s="56"/>
-      <c r="L5" s="57">
+      <c r="L5" s="57" t="e">
         <f t="shared" si="5"/>
-        <v>244063.10749679999</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -2585,18 +2629,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="56" t="e">
         <f t="shared" si="3"/>
-        <v>100542.16929570001</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J6" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K6" s="56"/>
-      <c r="L6" s="57">
+      <c r="L6" s="57" t="e">
         <f t="shared" si="5"/>
-        <v>100542.16929570001</v>
+        <v>#VALUE!</v>
       </c>
       <c r="O6" s="182"/>
     </row>
@@ -2628,18 +2672,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I7" s="56">
+      <c r="I7" s="56" t="e">
         <f t="shared" si="3"/>
-        <v>98612.377178700001</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J7" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K7" s="56"/>
-      <c r="L7" s="57">
+      <c r="L7" s="57" t="e">
         <f t="shared" si="5"/>
-        <v>98612.377178700001</v>
+        <v>#VALUE!</v>
       </c>
       <c r="O7" s="182"/>
     </row>
@@ -2669,18 +2713,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I8" s="56">
+      <c r="I8" s="56" t="e">
         <f t="shared" si="3"/>
-        <v>98226.418755300008</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J8" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K8" s="56"/>
-      <c r="L8" s="57">
+      <c r="L8" s="57" t="e">
         <f t="shared" si="5"/>
-        <v>98226.418755300008</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -2709,18 +2753,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I9" s="56">
+      <c r="I9" s="56" t="e">
         <f t="shared" si="3"/>
-        <v>98612.377178700001</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J9" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K9" s="56"/>
-      <c r="L9" s="57">
+      <c r="L9" s="57" t="e">
         <f t="shared" si="5"/>
-        <v>98612.377178700001</v>
+        <v>#VALUE!</v>
       </c>
       <c r="O9" s="182"/>
     </row>
@@ -2749,18 +2793,18 @@
         <v>0</v>
       </c>
       <c r="H10" s="191"/>
-      <c r="I10" s="191">
+      <c r="I10" s="191" t="e">
         <f t="shared" si="3"/>
-        <v>98226.418755300008</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J10" s="191">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K10" s="191"/>
-      <c r="L10" s="192">
+      <c r="L10" s="192" t="e">
         <f t="shared" si="5"/>
-        <v>98226.418755300008</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -2789,18 +2833,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I11" s="56">
+      <c r="I11" s="56" t="e">
         <f t="shared" si="3"/>
-        <v>97261.522696800006</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J11" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K11" s="56"/>
-      <c r="L11" s="57">
+      <c r="L11" s="57" t="e">
         <f t="shared" si="5"/>
-        <v>97261.522696800006</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -2829,18 +2873,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I12" s="56">
+      <c r="I12" s="56" t="e">
         <f t="shared" si="3"/>
-        <v>100542.16929570001</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J12" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K12" s="56"/>
-      <c r="L12" s="57">
+      <c r="L12" s="57" t="e">
         <f t="shared" si="5"/>
-        <v>100542.16929570001</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -2871,18 +2915,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I13" s="56">
+      <c r="I13" s="56" t="e">
         <f t="shared" si="3"/>
-        <v>98612.377178700001</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J13" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K13" s="56"/>
-      <c r="L13" s="57">
+      <c r="L13" s="57" t="e">
         <f t="shared" si="5"/>
-        <v>98612.377178700001</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -2913,18 +2957,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I14" s="66">
+      <c r="I14" s="66" t="e">
         <f t="shared" si="3"/>
-        <v>98226.418755300008</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J14" s="66">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K14" s="66"/>
-      <c r="L14" s="184">
+      <c r="L14" s="184" t="e">
         <f t="shared" si="5"/>
-        <v>98226.418755300008</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -2952,18 +2996,18 @@
         <f t="shared" si="2"/>
         <v>15331.019655845375</v>
       </c>
-      <c r="I15" s="56">
+      <c r="I15" s="56" t="e">
         <f t="shared" si="3"/>
-        <v>97261.522696800006</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J15" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K15" s="56"/>
-      <c r="L15" s="57">
+      <c r="L15" s="57" t="e">
         <f t="shared" si="5"/>
-        <v>495868.03374877974</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -2994,18 +3038,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I16" s="56">
+      <c r="I16" s="56" t="e">
         <f t="shared" si="3"/>
-        <v>100542.16929570001</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J16" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K16" s="56"/>
-      <c r="L16" s="57">
+      <c r="L16" s="57" t="e">
         <f t="shared" si="5"/>
-        <v>100542.16929570001</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -3034,18 +3078,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I17" s="56">
+      <c r="I17" s="56" t="e">
         <f t="shared" si="3"/>
-        <v>97261.522696800006</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J17" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K17" s="56"/>
-      <c r="L17" s="57">
+      <c r="L17" s="57" t="e">
         <f t="shared" si="5"/>
-        <v>97261.522696800006</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3074,18 +3118,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I18" s="56">
+      <c r="I18" s="56" t="e">
         <f t="shared" si="3"/>
-        <v>100542.16929570001</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J18" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K18" s="56"/>
-      <c r="L18" s="57">
+      <c r="L18" s="57" t="e">
         <f t="shared" si="5"/>
-        <v>100542.16929570001</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -3114,18 +3158,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I19" s="56">
+      <c r="I19" s="56" t="e">
         <f t="shared" si="3"/>
-        <v>142804.61665800001</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J19" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K19" s="56"/>
-      <c r="L19" s="57">
+      <c r="L19" s="57" t="e">
         <f t="shared" si="5"/>
-        <v>142804.61665800001</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="24" x14ac:dyDescent="0.25">
@@ -3151,18 +3195,18 @@
         <v>0</v>
       </c>
       <c r="H20" s="191"/>
-      <c r="I20" s="191">
+      <c r="I20" s="191" t="e">
         <f t="shared" si="3"/>
-        <v>20841.754863600003</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J20" s="191">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K20" s="191"/>
-      <c r="L20" s="192">
+      <c r="L20" s="192" t="e">
         <f t="shared" si="5"/>
-        <v>20841.754863600003</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -3191,18 +3235,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I21" s="56">
+      <c r="I21" s="56" t="e">
         <f t="shared" si="3"/>
-        <v>20841.754863600003</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J21" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K21" s="66"/>
-      <c r="L21" s="57">
+      <c r="L21" s="57" t="e">
         <f t="shared" si="5"/>
-        <v>20841.754863600003</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -3228,18 +3272,18 @@
         <f t="shared" si="2"/>
         <v>6534.8789836872129</v>
       </c>
-      <c r="I22" s="147">
+      <c r="I22" s="147" t="e">
         <f t="shared" si="3"/>
-        <v>20841.754863600003</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J22" s="147">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K22" s="147"/>
-      <c r="L22" s="148">
+      <c r="L22" s="148" t="e">
         <f t="shared" si="5"/>
-        <v>190748.60843946753</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -3268,18 +3312,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I23" s="56">
+      <c r="I23" s="56" t="e">
         <f t="shared" si="3"/>
-        <v>20841.754863600003</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J23" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K23" s="56"/>
-      <c r="L23" s="57">
+      <c r="L23" s="57" t="e">
         <f t="shared" si="5"/>
-        <v>20841.754863600003</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -3310,18 +3354,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I24" s="56">
+      <c r="I24" s="56" t="e">
         <f t="shared" si="3"/>
-        <v>20841.754863600003</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J24" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K24" s="56"/>
-      <c r="L24" s="57">
+      <c r="L24" s="57" t="e">
         <f t="shared" si="5"/>
-        <v>20841.754863600003</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -3350,18 +3394,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I25" s="56">
+      <c r="I25" s="56" t="e">
         <f t="shared" si="3"/>
-        <v>20841.754863600003</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J25" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K25" s="56"/>
-      <c r="L25" s="57">
+      <c r="L25" s="57" t="e">
         <f t="shared" si="5"/>
-        <v>20841.754863600003</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -3390,18 +3434,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I26" s="56">
+      <c r="I26" s="56" t="e">
         <f t="shared" si="3"/>
-        <v>20841.754863600003</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J26" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K26" s="56"/>
-      <c r="L26" s="57">
+      <c r="L26" s="57" t="e">
         <f t="shared" si="5"/>
-        <v>20841.754863600003</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -3430,18 +3474,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I27" s="56">
+      <c r="I27" s="56" t="e">
         <f t="shared" si="3"/>
-        <v>20841.754863600003</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J27" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K27" s="56"/>
-      <c r="L27" s="57">
+      <c r="L27" s="57" t="e">
         <f t="shared" si="5"/>
-        <v>20841.754863600003</v>
+        <v>#VALUE!</v>
       </c>
       <c r="O27" s="44">
         <f>F27+F26+F19</f>
@@ -3475,18 +3519,18 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I28" s="56">
+      <c r="I28" s="56" t="e">
         <f t="shared" si="3"/>
-        <v>20841.754863600003</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J28" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K28" s="56"/>
-      <c r="L28" s="57">
+      <c r="L28" s="57" t="e">
         <f t="shared" si="5"/>
-        <v>20841.754863600003</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3514,18 +3558,18 @@
         <f t="shared" si="2"/>
         <v>3285.2184976811513</v>
       </c>
-      <c r="I29" s="56">
+      <c r="I29" s="56" t="e">
         <f t="shared" si="3"/>
-        <v>20841.754863600003</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J29" s="56">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K29" s="56"/>
-      <c r="L29" s="57">
+      <c r="L29" s="57" t="e">
         <f t="shared" si="5"/>
-        <v>106257.43580330994</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -3559,80 +3603,80 @@
       </c>
       <c r="G31" s="77"/>
       <c r="H31" s="77"/>
-      <c r="I31" s="138">
+      <c r="I31" s="138" t="e">
         <f>SUM(I3:I30)</f>
-        <v>1929792.1170000006</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J31" s="138">
         <f>SUM(J3:J30)</f>
         <v>0</v>
       </c>
       <c r="K31" s="137"/>
-      <c r="L31" s="137">
+      <c r="L31" s="137" t="e">
         <f>SUM(L3:L29)</f>
-        <v>2730522.7473675553</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="J32" s="22"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="225" t="s">
+      <c r="A33" s="223" t="s">
         <v>136</v>
       </c>
-      <c r="B33" s="225"/>
-      <c r="C33" s="225"/>
-      <c r="D33" s="225"/>
-      <c r="E33" s="225"/>
-      <c r="F33" s="225"/>
-      <c r="G33" s="225"/>
-      <c r="H33" s="225"/>
-      <c r="I33" s="225"/>
-      <c r="J33" s="225"/>
-      <c r="K33" s="225"/>
-      <c r="L33" s="225"/>
+      <c r="B33" s="223"/>
+      <c r="C33" s="223"/>
+      <c r="D33" s="223"/>
+      <c r="E33" s="223"/>
+      <c r="F33" s="223"/>
+      <c r="G33" s="223"/>
+      <c r="H33" s="223"/>
+      <c r="I33" s="223"/>
+      <c r="J33" s="223"/>
+      <c r="K33" s="223"/>
+      <c r="L33" s="223"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="225"/>
-      <c r="B34" s="225"/>
-      <c r="C34" s="225"/>
-      <c r="D34" s="225"/>
-      <c r="E34" s="225"/>
-      <c r="F34" s="225"/>
-      <c r="G34" s="225"/>
-      <c r="H34" s="225"/>
-      <c r="I34" s="225"/>
-      <c r="J34" s="225"/>
-      <c r="K34" s="225"/>
-      <c r="L34" s="225"/>
+      <c r="A34" s="223"/>
+      <c r="B34" s="223"/>
+      <c r="C34" s="223"/>
+      <c r="D34" s="223"/>
+      <c r="E34" s="223"/>
+      <c r="F34" s="223"/>
+      <c r="G34" s="223"/>
+      <c r="H34" s="223"/>
+      <c r="I34" s="223"/>
+      <c r="J34" s="223"/>
+      <c r="K34" s="223"/>
+      <c r="L34" s="223"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="225"/>
-      <c r="B35" s="225"/>
-      <c r="C35" s="225"/>
-      <c r="D35" s="225"/>
-      <c r="E35" s="225"/>
-      <c r="F35" s="225"/>
-      <c r="G35" s="225"/>
-      <c r="H35" s="225"/>
-      <c r="I35" s="225"/>
-      <c r="J35" s="225"/>
-      <c r="K35" s="225"/>
-      <c r="L35" s="225"/>
+      <c r="A35" s="223"/>
+      <c r="B35" s="223"/>
+      <c r="C35" s="223"/>
+      <c r="D35" s="223"/>
+      <c r="E35" s="223"/>
+      <c r="F35" s="223"/>
+      <c r="G35" s="223"/>
+      <c r="H35" s="223"/>
+      <c r="I35" s="223"/>
+      <c r="J35" s="223"/>
+      <c r="K35" s="223"/>
+      <c r="L35" s="223"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="225"/>
-      <c r="B36" s="225"/>
-      <c r="C36" s="225"/>
-      <c r="D36" s="225"/>
-      <c r="E36" s="225"/>
-      <c r="F36" s="225"/>
-      <c r="G36" s="225"/>
-      <c r="H36" s="225"/>
-      <c r="I36" s="225"/>
-      <c r="J36" s="225"/>
-      <c r="K36" s="225"/>
-      <c r="L36" s="225"/>
+      <c r="A36" s="223"/>
+      <c r="B36" s="223"/>
+      <c r="C36" s="223"/>
+      <c r="D36" s="223"/>
+      <c r="E36" s="223"/>
+      <c r="F36" s="223"/>
+      <c r="G36" s="223"/>
+      <c r="H36" s="223"/>
+      <c r="I36" s="223"/>
+      <c r="J36" s="223"/>
+      <c r="K36" s="223"/>
+      <c r="L36" s="223"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E40" s="21"/>
@@ -3672,22 +3716,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="218" t="s">
+      <c r="A1" s="225" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
-      <c r="H1" s="219"/>
-      <c r="I1" s="219"/>
-      <c r="J1" s="219"/>
-      <c r="K1" s="219"/>
-      <c r="L1" s="219"/>
-      <c r="M1" s="219"/>
-      <c r="N1" s="220"/>
+      <c r="B1" s="226"/>
+      <c r="C1" s="226"/>
+      <c r="D1" s="226"/>
+      <c r="E1" s="226"/>
+      <c r="F1" s="226"/>
+      <c r="G1" s="226"/>
+      <c r="H1" s="226"/>
+      <c r="I1" s="226"/>
+      <c r="J1" s="226"/>
+      <c r="K1" s="226"/>
+      <c r="L1" s="226"/>
+      <c r="M1" s="226"/>
+      <c r="N1" s="227"/>
       <c r="O1" s="78"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
@@ -3825,11 +3869,11 @@
         <f>C8-J38</f>
         <v>-196408.73539999995</v>
       </c>
-      <c r="L8" s="222">
+      <c r="L8" s="229">
         <f>C7-J38</f>
         <v>502773.47460000002</v>
       </c>
-      <c r="M8" s="222"/>
+      <c r="M8" s="229"/>
       <c r="N8" s="86"/>
       <c r="O8" s="80"/>
       <c r="P8" s="11"/>
@@ -3929,9 +3973,9 @@
         <f>J10+L10</f>
         <v>46718.769952059985</v>
       </c>
-      <c r="O10" s="99">
+      <c r="O10" s="99" t="e">
         <f>N10+'prorrateo '!L3</f>
-        <v>145331.14713075999</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P10" s="11"/>
     </row>
@@ -3985,9 +4029,9 @@
         <f t="shared" ref="N11:N25" si="5">J11+L11</f>
         <v>48175.079457140018</v>
       </c>
-      <c r="O11" s="99">
+      <c r="O11" s="99" t="e">
         <f>N11+'prorrateo '!L4</f>
-        <v>146401.49821244003</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P11" s="11"/>
     </row>
@@ -4041,9 +4085,9 @@
         <f t="shared" si="5"/>
         <v>28134.635719839996</v>
       </c>
-      <c r="O12" s="99">
+      <c r="O12" s="99" t="e">
         <f>N12+'prorrateo '!L5</f>
-        <v>272197.74321663997</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P12" s="11"/>
       <c r="S12">
@@ -4100,9 +4144,9 @@
         <f t="shared" si="5"/>
         <v>33453.61182666001</v>
       </c>
-      <c r="O13" s="99">
+      <c r="O13" s="99" t="e">
         <f>N13+'prorrateo '!L6</f>
-        <v>133995.78112236003</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P13" s="11"/>
     </row>
@@ -4156,9 +4200,9 @@
         <f t="shared" si="5"/>
         <v>31506.518552060003</v>
       </c>
-      <c r="O14" s="99">
+      <c r="O14" s="99" t="e">
         <f>N14+'prorrateo '!L7</f>
-        <v>130118.89573076001</v>
+        <v>#VALUE!</v>
       </c>
       <c r="P14" s="11"/>
     </row>
@@ -4212,9 +4256,9 @@
         <f t="shared" si="5"/>
         <v>35973.390757140027</v>
       </c>
-      <c r="O15" s="99">
+      <c r="O15" s="99" t="e">
         <f>N15+'prorrateo '!L8</f>
-        <v>134199.80951244003</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -4267,9 +4311,9 @@
         <f t="shared" si="5"/>
         <v>33447.909452060027</v>
       </c>
-      <c r="O16" s="99">
+      <c r="O16" s="99" t="e">
         <f>N16+'prorrateo '!L9</f>
-        <v>132060.28663076003</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -4322,9 +4366,9 @@
         <f t="shared" si="5"/>
         <v>27888.951357140002</v>
       </c>
-      <c r="O17" s="99">
+      <c r="O17" s="99" t="e">
         <f>N17+'prorrateo '!L10</f>
-        <v>126115.37011244001</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -4377,9 +4421,9 @@
         <f t="shared" si="5"/>
         <v>34043.216719839998</v>
       </c>
-      <c r="O18" s="99">
+      <c r="O18" s="99" t="e">
         <f>N18+'prorrateo '!L11</f>
-        <v>131304.73941664002</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4432,9 +4476,9 @@
         <f t="shared" si="5"/>
         <v>50897.993826659964</v>
       </c>
-      <c r="O19" s="99">
+      <c r="O19" s="99" t="e">
         <f>N19+'prorrateo '!L12</f>
-        <v>151440.16312235995</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4487,9 +4531,9 @@
         <f t="shared" si="5"/>
         <v>45039.982652060018</v>
       </c>
-      <c r="O20" s="99">
+      <c r="O20" s="99" t="e">
         <f>N20+'prorrateo '!L13</f>
-        <v>143652.35983076002</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -4542,9 +4586,9 @@
         <f t="shared" si="5"/>
         <v>36039.041657140013</v>
       </c>
-      <c r="O21" s="99">
+      <c r="O21" s="99" t="e">
         <f>N21+'prorrateo '!L14</f>
-        <v>134265.46041244001</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -4597,9 +4641,9 @@
         <f t="shared" si="5"/>
         <v>30094.784019839986</v>
       </c>
-      <c r="O22" s="99">
+      <c r="O22" s="99" t="e">
         <f>N22+'prorrateo '!L15</f>
-        <v>525962.81776861975</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -4652,9 +4696,9 @@
         <f t="shared" si="5"/>
         <v>37008.139126660019</v>
       </c>
-      <c r="O23" s="99">
+      <c r="O23" s="99" t="e">
         <f>N23+'prorrateo '!L16</f>
-        <v>137550.30842236002</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -4707,9 +4751,9 @@
         <f t="shared" si="5"/>
         <v>30141.677519840006</v>
       </c>
-      <c r="O24" s="99">
+      <c r="O24" s="99" t="e">
         <f>N24+'prorrateo '!L17</f>
-        <v>127403.20021664002</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -4762,9 +4806,9 @@
         <f t="shared" si="5"/>
         <v>33303.552626659992</v>
       </c>
-      <c r="O25" s="99">
+      <c r="O25" s="99" t="e">
         <f>N25+'prorrateo '!L18</f>
-        <v>133845.72192236001</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -4817,9 +4861,9 @@
         <f>J26+L26</f>
         <v>63015.419520399897</v>
       </c>
-      <c r="O26" s="99">
+      <c r="O26" s="99" t="e">
         <f>N26+'prorrateo '!L19</f>
-        <v>205820.03617839993</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4861,9 +4905,9 @@
         <f t="shared" ref="N27:N37" si="6">J27+L27</f>
         <v>5429.9535256800009</v>
       </c>
-      <c r="O27" s="99">
+      <c r="O27" s="99" t="e">
         <f>N27+'prorrateo '!L20</f>
-        <v>26271.708389280004</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -4900,9 +4944,9 @@
         <f t="shared" si="6"/>
         <v>5429.9535256800009</v>
       </c>
-      <c r="O28" s="99">
+      <c r="O28" s="99" t="e">
         <f>N28+'prorrateo '!L21</f>
-        <v>26271.708389280004</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -4932,9 +4976,9 @@
         <f t="shared" si="6"/>
         <v>5429.9535256800009</v>
       </c>
-      <c r="O29" s="99">
+      <c r="O29" s="99" t="e">
         <f>N29+'prorrateo '!L22</f>
-        <v>196178.56196514753</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -4964,9 +5008,9 @@
         <f t="shared" si="6"/>
         <v>5429.9535256800009</v>
       </c>
-      <c r="O30" s="99">
+      <c r="O30" s="99" t="e">
         <f>N30+'prorrateo '!L23</f>
-        <v>26271.708389280004</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -4996,9 +5040,9 @@
         <f t="shared" si="6"/>
         <v>5429.9535256800009</v>
       </c>
-      <c r="O31" s="99">
+      <c r="O31" s="99" t="e">
         <f>N31+'prorrateo '!L24</f>
-        <v>26271.708389280004</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -5028,9 +5072,9 @@
         <f t="shared" si="6"/>
         <v>5429.9535256800009</v>
       </c>
-      <c r="O32" s="99">
+      <c r="O32" s="99" t="e">
         <f>N32+'prorrateo '!L25</f>
-        <v>26271.708389280004</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -5060,9 +5104,9 @@
         <f t="shared" si="6"/>
         <v>5429.9535256800009</v>
       </c>
-      <c r="O33" s="99">
+      <c r="O33" s="99" t="e">
         <f>N33+'prorrateo '!L26</f>
-        <v>26271.708389280004</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -5092,9 +5136,9 @@
         <f t="shared" si="6"/>
         <v>5429.9535256800009</v>
       </c>
-      <c r="O34" s="99">
+      <c r="O34" s="99" t="e">
         <f>N34+'prorrateo '!L27</f>
-        <v>26271.708389280004</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -5131,9 +5175,9 @@
         <f t="shared" si="6"/>
         <v>5429.9535256800009</v>
       </c>
-      <c r="O35" s="99">
+      <c r="O35" s="99" t="e">
         <f>N35+'prorrateo '!L28</f>
-        <v>26271.708389280004</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -5170,9 +5214,9 @@
         <f t="shared" si="6"/>
         <v>5429.9535256800009</v>
       </c>
-      <c r="O36" s="99">
+      <c r="O36" s="99" t="e">
         <f>N36+'prorrateo '!L29</f>
-        <v>111687.38932898994</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -5262,18 +5306,18 @@
       <c r="A40" s="97" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="221"/>
-      <c r="D40" s="219"/>
-      <c r="E40" s="219"/>
-      <c r="F40" s="219"/>
-      <c r="G40" s="219"/>
-      <c r="H40" s="219"/>
-      <c r="I40" s="219"/>
-      <c r="J40" s="219"/>
-      <c r="K40" s="219"/>
-      <c r="L40" s="219"/>
-      <c r="M40" s="219"/>
-      <c r="N40" s="219"/>
+      <c r="C40" s="228"/>
+      <c r="D40" s="226"/>
+      <c r="E40" s="226"/>
+      <c r="F40" s="226"/>
+      <c r="G40" s="226"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="226"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="226"/>
+      <c r="M40" s="226"/>
+      <c r="N40" s="226"/>
       <c r="O40" s="97"/>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
